--- a/datos/Practica Test.xlsx
+++ b/datos/Practica Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorge/Desktop/AUTOESCUELA/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753B7945-B8AC-8741-999F-77464F829E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BCDDD3-F0E7-8540-A25A-26BBC2C99E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="23220" windowHeight="16820" xr2:uid="{AE6512D7-AD52-4543-8CDE-87DCF5042393}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="T20" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20'!$A$1:$E$391</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20'!$A$1:$E$431</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="962">
   <si>
     <t>Pregunta</t>
   </si>
@@ -506,9 +506,6 @@
     <t>imagenes/PT15082602.png</t>
   </si>
   <si>
-    <t>3. Si el conductor del ciclomotor decide adelantar al tractor, debe de tener en cuenta que...</t>
-  </si>
-  <si>
     <t xml:space="preserve">imagenes/PT15082603.png  </t>
   </si>
   <si>
@@ -629,9 +626,6 @@
     <t xml:space="preserve">imagenes/PT15082623.png  </t>
   </si>
   <si>
-    <t>24. ¿Qué tanto por ciento de muertes evita el cinturón de seguridad cuando se circula a gran velocidad?</t>
-  </si>
-  <si>
     <t xml:space="preserve">imagenes/PT15082624.png  </t>
   </si>
   <si>
@@ -1448,123 +1442,33 @@
     <t>El sistema RCTA.</t>
   </si>
   <si>
-    <t>1. Circulando con lluvia muy intensa, ¿es correcto encender la luz antiniebla trasera?</t>
-  </si>
-  <si>
-    <t>2. Para que pueda circular un ciclomotor, ¿es obligatorio que esté asegurado?</t>
-  </si>
-  <si>
-    <t>3. Los conductores jóvenes suelen tener más accidentes...</t>
-  </si>
-  <si>
-    <t>4. La vía, su entorno y el propio vehículo, ¿pueden favorecer la aparición de distracciones al volante?</t>
-  </si>
-  <si>
-    <t>5. Esta señalización recomienda circular a 70 kilómetros por hora...</t>
-  </si>
-  <si>
     <t>imagenes/70niebla.png</t>
   </si>
   <si>
-    <t>6. Al adelantar al ciclista que aparece en la fotografía, ¿es obligatorio invadir el carril de sentido contrario de la calzada?</t>
-  </si>
-  <si>
     <t>imagenes/bicir.png</t>
   </si>
   <si>
-    <t>7. La distancia de detención puede variar en función...</t>
-  </si>
-  <si>
-    <t>8. Ante un paso a nivel cuyas barreras están en movimiento, ¿es obligatorio detenerse?</t>
-  </si>
-  <si>
     <t>imagenes/pasonivel.png</t>
   </si>
   <si>
-    <t>9. ¿Está permitido que un vehículo circule sin silenciador de explosiones?</t>
-  </si>
-  <si>
     <t>imagenes/tuboes.png</t>
   </si>
   <si>
-    <t>10. ¿Está correctamente inmovilizada esta furgoneta?</t>
-  </si>
-  <si>
     <t>imagenes/furgomal.png</t>
   </si>
   <si>
-    <t>11. Los ciclomotores de dos ruedas deben llevar...</t>
-  </si>
-  <si>
-    <t>12. En un tramo de vía con la señal "túnel", ¿está permitido hacer un cambio de sentido?</t>
-  </si>
-  <si>
-    <t>13. ¿Cuál es la velocidad máxima genérica para un turismo en autovía?</t>
-  </si>
-  <si>
-    <t>14. ¿Cuándo debe comprobar el reglaje de los espejos retrovisores?</t>
-  </si>
-  <si>
-    <t>15. El conductor está obligado a advertir mediante señales ópticas...</t>
-  </si>
-  <si>
-    <t>16. Para seguir de frente, ¿dónde hay que detenerse?</t>
-  </si>
-  <si>
     <t>imagenes/semaforcru.png</t>
   </si>
   <si>
-    <t>17. Si padece una alergia respiratoria, debe tener en cuenta que...</t>
-  </si>
-  <si>
-    <t>18. Circulando observa que se aproxima una ambulancia en servicio urgente. Debe tener en cuenta que...</t>
-  </si>
-  <si>
-    <t>19. ¿Puede circular con su motocicleta por un carril bus?</t>
-  </si>
-  <si>
-    <t>20. La mejor forma de recuperarse de la fatiga cuando se conduce, es...</t>
-  </si>
-  <si>
-    <t>21. La carga transportada en un vehículo, debe estar dispuesta de forma que...</t>
-  </si>
-  <si>
-    <t>22. ¿Qué indican estas señales?</t>
-  </si>
-  <si>
     <t>imagenes/curvass.png</t>
   </si>
   <si>
-    <t>23. ¿Qué indica la señal?</t>
-  </si>
-  <si>
     <t>imagenes/ciclo31.png</t>
   </si>
   <si>
-    <t>24. En una vía urbana de sentido único, si los carriles no están delimitados por marcas viales, ¿por dónde está obligado a circular el conductor de un turismo?</t>
-  </si>
-  <si>
-    <t>25. En caso de contradicción entre señales del mismo tipo, ¿cuál prevalecerá?</t>
-  </si>
-  <si>
-    <t>26. Si el vehículo de detrás se acerca demasiado, es conveniente...</t>
-  </si>
-  <si>
-    <t>27. Cuando llueve o hay viento, ¿por qué hay que tener más precaución con los ciclistas?</t>
-  </si>
-  <si>
-    <t>28. En esta curva pisa el freno muy fuerte. ¿Hay peligro?</t>
-  </si>
-  <si>
     <t>imagenes/curvar.png</t>
   </si>
   <si>
-    <t>29. Al adelantar a un peatón, es obligatorio dejar una separación lateral mínima de 1,50 metros cuando circule...</t>
-  </si>
-  <si>
-    <t>30. Esta señal indica peligro por la proximidad de...</t>
-  </si>
-  <si>
     <t>imagenes/dangecur.png</t>
   </si>
   <si>
@@ -2052,19 +1956,1000 @@
   </si>
   <si>
     <t>Solo los ciclomotores</t>
+  </si>
+  <si>
+    <t>Esta señal indica peligro por la proximidad de...</t>
+  </si>
+  <si>
+    <t>Al adelantar a un peatón, es obligatorio dejar una separación lateral mínima de 1,50 metros cuando circule...</t>
+  </si>
+  <si>
+    <t>En esta curva pisa el freno muy fuerte. ¿Hay peligro?</t>
+  </si>
+  <si>
+    <t>Cuando llueve o hay viento, ¿por qué hay que tener más precaución con los ciclistas?</t>
+  </si>
+  <si>
+    <t>Si el vehículo de detrás se acerca demasiado, es conveniente...</t>
+  </si>
+  <si>
+    <t>En caso de contradicción entre señales del mismo tipo, ¿cuál prevalecerá?</t>
+  </si>
+  <si>
+    <t>¿Qué tanto por ciento de muertes evita el cinturón de seguridad cuando se circula a gran velocidad?</t>
+  </si>
+  <si>
+    <t>En una vía urbana de sentido único, si los carriles no están delimitados por marcas viales, ¿por dónde está obligado a circular el conductor de un turismo?</t>
+  </si>
+  <si>
+    <t>¿Qué indican estas señales?</t>
+  </si>
+  <si>
+    <t>La carga transportada en un vehículo, debe estar dispuesta de forma que...</t>
+  </si>
+  <si>
+    <t>La mejor forma de recuperarse de la fatiga cuando se conduce, es...</t>
+  </si>
+  <si>
+    <t>¿Puede circular con su motocicleta por un carril bus?</t>
+  </si>
+  <si>
+    <t>Circulando observa que se aproxima una ambulancia en servicio urgente. Debe tener en cuenta que...</t>
+  </si>
+  <si>
+    <t>Si padece una alergia respiratoria, debe tener en cuenta que...</t>
+  </si>
+  <si>
+    <t>Para seguir de frente, ¿dónde hay que detenerse?</t>
+  </si>
+  <si>
+    <t>El conductor está obligado a advertir mediante señales ópticas...</t>
+  </si>
+  <si>
+    <t>¿Cuándo debe comprobar el reglaje de los espejos retrovisores?</t>
+  </si>
+  <si>
+    <t>¿Cuál es la velocidad máxima genérica para un turismo en autovía?</t>
+  </si>
+  <si>
+    <t>En un tramo de vía con la señal "túnel", ¿está permitido hacer un cambio de sentido?</t>
+  </si>
+  <si>
+    <t>Los ciclomotores de dos ruedas deben llevar...</t>
+  </si>
+  <si>
+    <t>¿Está correctamente inmovilizada esta furgoneta?</t>
+  </si>
+  <si>
+    <t>¿Está permitido que un vehículo circule sin silenciador de explosiones?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ante un paso a nivel cuyas barreras están en movimiento, ¿es obligatorio detenerse?</t>
+  </si>
+  <si>
+    <t>La distancia de detención puede variar en función...</t>
+  </si>
+  <si>
+    <t>Al adelantar al ciclista que aparece en la fotografía, ¿es obligatorio invadir el carril de sentido contrario de la calzada?</t>
+  </si>
+  <si>
+    <t>Esta señalización recomienda circular a 70 kilómetros por hora...</t>
+  </si>
+  <si>
+    <t>Si el conductor del ciclomotor decide adelantar al tractor, debe de tener en cuenta que...</t>
+  </si>
+  <si>
+    <t>Los conductores jóvenes suelen tener más accidentes...</t>
+  </si>
+  <si>
+    <t>Para que pueda circular un ciclomotor, ¿es obligatorio que esté asegurado?</t>
+  </si>
+  <si>
+    <t>Circulando con lluvia muy intensa, ¿es correcto encender la luz antiniebla trasera?</t>
+  </si>
+  <si>
+    <t>¿Cuál de los siguientes NO corresponde a un nivel de dificultad ante la circulación con nieve?</t>
+  </si>
+  <si>
+    <t>Nivel verde</t>
+  </si>
+  <si>
+    <t>Nivel amarillo</t>
+  </si>
+  <si>
+    <t>Nivel rosa</t>
+  </si>
+  <si>
+    <t>¿Por qué razón el momento de mayor peligro al conducir con lluvia es cuando empiezan a caer las primeras gotas?</t>
+  </si>
+  <si>
+    <t>Porque el agua se mezcla con el polvo y la grasa y la calzada se vuelve mas deslizante.</t>
+  </si>
+  <si>
+    <t>Porque los parabrisas no comienzan a funcionar hasta que existe lluvia intensa.</t>
+  </si>
+  <si>
+    <t>Porque esas pequeñas gotas dificultan la visibilidad en el cristal delantero.</t>
+  </si>
+  <si>
+    <t>¿Qué relación de marcha es la que transmite menos fuerza al vehículo?</t>
+  </si>
+  <si>
+    <t>La primera marcha</t>
+  </si>
+  <si>
+    <t>La marcha más alta</t>
+  </si>
+  <si>
+    <t>La segunda o la tercera marcha depende del vehiculo que utilicemos</t>
+  </si>
+  <si>
+    <t>¿Cuál es la velocidad máxima a la que puede circular una bicicleta fuera de poblado?</t>
+  </si>
+  <si>
+    <t>45 km/hora, excepto en aquellos tramos de via en que sea posible desarrollar una velocidad superior</t>
+  </si>
+  <si>
+    <t>40 km/hora, excepto en aquellos tramos de via en que sea posible desarrollar una velocidad superior</t>
+  </si>
+  <si>
+    <t>50 km/hora, excepto en aquellos tramos de via en que sea posible desarrollar una velocidad superior</t>
+  </si>
+  <si>
+    <t>¿Cuáles son las ruedas del vehículo que marcan el trazado de una curva?</t>
+  </si>
+  <si>
+    <t>Ruedas motrices</t>
+  </si>
+  <si>
+    <t>Ruedas directrices</t>
+  </si>
+  <si>
+    <t>Rueda de repuesto</t>
+  </si>
+  <si>
+    <t>Un vehículo dispone de "servofreno". ¿Qué sucede cuando se apaga el motor?</t>
+  </si>
+  <si>
+    <t>Que las ruedas se bloquean.</t>
+  </si>
+  <si>
+    <t>Que el freno de mano no funciona bien y tengo que tirar de la palanca con más fuerza.</t>
+  </si>
+  <si>
+    <t>Que el freno de pie no funciona bien y tengo que pisar el pedal con más fuerza.</t>
+  </si>
+  <si>
+    <t>Los espejos retrovisores exteriores de un vehículo, por lo general, ¿qué forma presentan?</t>
+  </si>
+  <si>
+    <t>Convexos</t>
+  </si>
+  <si>
+    <t>Planos</t>
+  </si>
+  <si>
+    <t>Cóncavos</t>
+  </si>
+  <si>
+    <t>En un túnel, el conductor de una motocicleta, si no tiene intención de adelantar al vehículo que va delante, ¿qué distancia debe mantener con él?</t>
+  </si>
+  <si>
+    <t>Al menos, 100 metros.</t>
+  </si>
+  <si>
+    <t>Al menos, 50 metros.</t>
+  </si>
+  <si>
+    <t>Al menos, 150 metros.</t>
+  </si>
+  <si>
+    <t>imagenes/p33.png</t>
+  </si>
+  <si>
+    <t>¿Qué advierte esta señal?</t>
+  </si>
+  <si>
+    <t>Visibilidad reducida.</t>
+  </si>
+  <si>
+    <t>Proyección de gravilla.</t>
+  </si>
+  <si>
+    <t>Obstrucción en la calzada.</t>
+  </si>
+  <si>
+    <t>el vehículo que baja.</t>
+  </si>
+  <si>
+    <t>En un tramo de via estrecho y con gran pendiente, ¿qué vehículo tiene que ceder el paso?</t>
+  </si>
+  <si>
+    <t>el vehículo más ligero.</t>
+  </si>
+  <si>
+    <t>el vehículo que sube.</t>
+  </si>
+  <si>
+    <t>Un herido presenta quemaduras, ¿ qué es lo que se debe hacer?</t>
+  </si>
+  <si>
+    <t>Quitarle la ropa pegada a la quemadura.</t>
+  </si>
+  <si>
+    <t>Limpiar la herida.</t>
+  </si>
+  <si>
+    <t>Tapar la quemadura con gasas húmedas.</t>
+  </si>
+  <si>
+    <t>En esta vía se ha dispuesto un carril adicional, ¿a qué velocidad máxima podrá circular el vehículo naranja?</t>
+  </si>
+  <si>
+    <t>A 80 kilómetros por hora.</t>
+  </si>
+  <si>
+    <t>A la genérica de la vía.</t>
+  </si>
+  <si>
+    <t>A 60 kilómetros por hora.</t>
+  </si>
+  <si>
+    <t>imágenes/carriladd.png</t>
+  </si>
+  <si>
+    <t>La luz antiniebla trasera deberá utilizarse siempre que...</t>
+  </si>
+  <si>
+    <t>circule por un puerto de montaña.</t>
+  </si>
+  <si>
+    <t>circule por un túnel.</t>
+  </si>
+  <si>
+    <t>circule con fuerte nevada.</t>
+  </si>
+  <si>
+    <t>Documentación del automóvil. Para circular con un turismo, ¿qué documentos se necesitan en todo caso, además del permiso de conducción?</t>
+  </si>
+  <si>
+    <t>El Impuesto de Vehículos de Tracción Mecánica (Impuesto Municipal de Circulación) del año en curso.</t>
+  </si>
+  <si>
+    <t>El Permiso de Circulación solamente.</t>
+  </si>
+  <si>
+    <t>El Permiso de Circulación y la Tarjeta de Inspección Técnica.</t>
+  </si>
+  <si>
+    <t>¿Debe el conductor del turismo de color blanco respetar la señal de stop cuando llegue al cruce?</t>
+  </si>
+  <si>
+    <t>Sí, debe respetar las marcas viales existentes.</t>
+  </si>
+  <si>
+    <t>No, porque la señal horizontal solo es para los que giren a la izquierda.</t>
+  </si>
+  <si>
+    <t>Sí, pero solo si sigue de frente.</t>
+  </si>
+  <si>
+    <t>imagenes/202608191.png</t>
+  </si>
+  <si>
+    <t>Si mientras circula se le pincha una rueda, ¿qué debe hacer?</t>
+  </si>
+  <si>
+    <t>Continuar circulando hasta llegar al taller más próximo.</t>
+  </si>
+  <si>
+    <t>Inmovilizar rápidamente el vehículo fuera de la calzada o en lugar seguro.</t>
+  </si>
+  <si>
+    <t>Detener el vehículo rápidamente en cualquier lugar y abandonarlo.</t>
+  </si>
+  <si>
+    <t>Durante la conducción, la fatiga...</t>
+  </si>
+  <si>
+    <t>hace que aumenten los errores de forma considerable.</t>
+  </si>
+  <si>
+    <t>facilita la percepción de las señales de tráfico.</t>
+  </si>
+  <si>
+    <t>hace que disminuyan los errores de forma considerable.</t>
+  </si>
+  <si>
+    <t>Un semáforo con línea blanca horizontal sobre fondo negro...</t>
+  </si>
+  <si>
+    <t>permite el paso a autobuses y tranvías.</t>
+  </si>
+  <si>
+    <t>prohíbe el paso a autobuses de líneas regulares y tranvías.</t>
+  </si>
+  <si>
+    <t>permite girar a la derecha y a la izquierda a autobuses y tranvías.</t>
+  </si>
+  <si>
+    <t>imagenes/202608192.png</t>
+  </si>
+  <si>
+    <t>La línea de borde de la calzada es discontinua; ¿está permitido estacionar en la parte transitable del arcén?</t>
+  </si>
+  <si>
+    <t>Sí, porque la línea es discontinua.</t>
+  </si>
+  <si>
+    <t>Solo para cargar o descargar mercancías.</t>
+  </si>
+  <si>
+    <t>imagenes/202608193.png</t>
+  </si>
+  <si>
+    <t>¿Puede perder el control del vehículo si circula con los amortiguadores en mal estado?</t>
+  </si>
+  <si>
+    <t>No, sin embargo, los cambios de marcha se realizarán con mayor dificultad debido a las oscilaciones del vehículo.</t>
+  </si>
+  <si>
+    <t>Sí, porque la distancia de frenado disminuirá, especialmente con el firme irregular o mojado.</t>
+  </si>
+  <si>
+    <t>Sí, porque el vehículo puede experimentar una inclinación excesiva al tomar las curvas.</t>
+  </si>
+  <si>
+    <t>Si observa que un vehículo quiere incorporarse por el carril de aceleración, ¿qué debe hacer?</t>
+  </si>
+  <si>
+    <t>Nada, porque tengo preferencia.</t>
+  </si>
+  <si>
+    <t>Cederle el paso</t>
+  </si>
+  <si>
+    <t>Facilitarle la incorporación en la medida de lo posible.</t>
+  </si>
+  <si>
+    <t>No deberá iniciar un adelantamiento sin comprobar previamente que...</t>
+  </si>
+  <si>
+    <t>existe espacio suficiente para volver al carril derecho cuando termine la maniobra.</t>
+  </si>
+  <si>
+    <t>los vehículos que circulan detrás mantienen la distancia de seguridad.</t>
+  </si>
+  <si>
+    <t>el vehículo de delante reduce su velocidad para facilitar la maniobra.</t>
+  </si>
+  <si>
+    <t>¿Cuál de las siguientes es una de las principales funciones del airbag en caso de accidente?</t>
+  </si>
+  <si>
+    <t>Evitar el efecto submarino.</t>
+  </si>
+  <si>
+    <t>Reducir el riesgo de heridas en la cara producidas por fragmentos de cristal procedentes del parabrisas.</t>
+  </si>
+  <si>
+    <t>Evitar que la columna de dirección golpee al conductor.</t>
+  </si>
+  <si>
+    <t>¿En qué tipo de vías se debe mantener la distancia de seguridad?</t>
+  </si>
+  <si>
+    <t>Solo en calzadas con dos sentidos de circulación.</t>
+  </si>
+  <si>
+    <t>Solo en calzadas en mal estado.</t>
+  </si>
+  <si>
+    <t>En todo tipo de vías.</t>
+  </si>
+  <si>
+    <t>En una vía se observa esta señal. ¿Qué vehículos están obligados a circular por dicha vía?</t>
+  </si>
+  <si>
+    <t>Las motocicletas sin sidecar.</t>
+  </si>
+  <si>
+    <t>Todas las motocicletas.</t>
+  </si>
+  <si>
+    <t>Todos los vehículos de dos ruedas.</t>
+  </si>
+  <si>
+    <t>¿Qué se considera como la distancia visible sin obstáculos previsibles?</t>
+  </si>
+  <si>
+    <t>Una zona de seguridad</t>
+  </si>
+  <si>
+    <t>Una zona de peligro extremo</t>
+  </si>
+  <si>
+    <t>Una zona restringida al paso de vehículos</t>
+  </si>
+  <si>
+    <t>¿A qué distancia, en metros, deben poder verse las luces de un vehículo prioritario?</t>
+  </si>
+  <si>
+    <t>A 10 metros</t>
+  </si>
+  <si>
+    <t>A 50 metros</t>
+  </si>
+  <si>
+    <t>A 100 metros</t>
+  </si>
+  <si>
+    <t>¿Se permite desplazarse utilizando únicamente el encendido de posición del vehículo entre el atardecer y el amanecer?</t>
+  </si>
+  <si>
+    <t>Sí, en todo tipo de vias mientras estén suficientemente iluminadas.</t>
+  </si>
+  <si>
+    <t>No, también debes utilizar, como mínimo, el alumbrado de corto alcance.</t>
+  </si>
+  <si>
+    <t>Sí, en vías urbanas suficientemente iluminadas.</t>
+  </si>
+  <si>
+    <t>¿En cuánto porcentaje aumentará el consumo de carburante si conducimos de manera agresiva?</t>
+  </si>
+  <si>
+    <t>50 % más de carburante</t>
+  </si>
+  <si>
+    <t>20 % más de carburante</t>
+  </si>
+  <si>
+    <t>80 % más de carburante</t>
+  </si>
+  <si>
+    <t>¿Cuál de los siguientes elementos NO tóxicos emite un vehículo estándar?</t>
+  </si>
+  <si>
+    <t>Óxido de Hierro.</t>
+  </si>
+  <si>
+    <t>Óxido de Magnesio.</t>
+  </si>
+  <si>
+    <t>Dióxido de Carbono.</t>
+  </si>
+  <si>
+    <t>¿Además de lubricar las partes en rozamiento, para qué más sirve el aceite en un vehículo?</t>
+  </si>
+  <si>
+    <t>Para tensar las correas del motor</t>
+  </si>
+  <si>
+    <t>Para refrigerar las partes del vehículo</t>
+  </si>
+  <si>
+    <t>Para evitar las pérdidas de fluido refrigerante</t>
+  </si>
+  <si>
+    <t>¿Qué acción de las siguientes puede suponer una distracción para el conductor?</t>
+  </si>
+  <si>
+    <t>Accionar el lavaparabrisas.</t>
+  </si>
+  <si>
+    <t>Mirar por el retrovisor.</t>
+  </si>
+  <si>
+    <t>Consultar el GPS.</t>
+  </si>
+  <si>
+    <t>A efectos de la normal utilización, no se tendrán en cuenta los carriles...</t>
+  </si>
+  <si>
+    <t>especiales.</t>
+  </si>
+  <si>
+    <t>reservados a determinados vehículos.</t>
+  </si>
+  <si>
+    <t>reversibles.</t>
+  </si>
+  <si>
+    <t>Pueden tener efectos negativos para la conducción.</t>
+  </si>
+  <si>
+    <t>Los medicamentos que se pueden adquirir sin receta médica...</t>
+  </si>
+  <si>
+    <t>No son peligrosos para la conducción.</t>
+  </si>
+  <si>
+    <t>Deben evitarse completamente.</t>
+  </si>
+  <si>
+    <t>¿Esta señal nos obliga a detener el vehículo?</t>
+  </si>
+  <si>
+    <t>Sí, cuando el vehículo al que nos aproximamos obstruya la vía.</t>
+  </si>
+  <si>
+    <t>Si, siempre.</t>
+  </si>
+  <si>
+    <t>imagenes/202608194.png</t>
+  </si>
+  <si>
+    <t>Un tractor que lleva un remolque, ¿qué velocidad máxima no puede superar fuera de poblado?</t>
+  </si>
+  <si>
+    <t>40 kilómetros por hora.</t>
+  </si>
+  <si>
+    <t>70 kilómetros por hora.</t>
+  </si>
+  <si>
+    <t>25 kilómetros por hora.</t>
+  </si>
+  <si>
+    <t>Las operaciones de carga y descarga deben efectuarse...</t>
+  </si>
+  <si>
+    <t>depositando la mercancía en la calzada para agilizar el trabajo.</t>
+  </si>
+  <si>
+    <t>respetando siempre las normas de parada y estacionamiento.</t>
+  </si>
+  <si>
+    <t>únicamente por el lado derecho de la calzada.</t>
+  </si>
+  <si>
+    <t>¿Hay que facilitar y ceder el paso a los vehículos que se aproximan por la derecha cuando no existe señalización de prioridad de paso?</t>
+  </si>
+  <si>
+    <t>No, porque los vehiculos que circulan por la via principall siempre tendrán prioridad.</t>
+  </si>
+  <si>
+    <t>Si, pero solamente a los autobuses.</t>
+  </si>
+  <si>
+    <t>Sí, de forma obligatoria.</t>
+  </si>
+  <si>
+    <t>La maniobra de marcha atrás debe realizarse...</t>
+  </si>
+  <si>
+    <t>Lo más rápido posible.</t>
+  </si>
+  <si>
+    <t>Con la máxima precaución.</t>
+  </si>
+  <si>
+    <t>Advirtiéndolo previamente con la señal de emergencia.</t>
+  </si>
+  <si>
+    <t>¿Cuál de los siguientes factores aumenta el tiempo de reacción cuando se va al volante?</t>
+  </si>
+  <si>
+    <t>Las comidas ligeras y ricas en minerales.</t>
+  </si>
+  <si>
+    <t>Mantener el vehículo fresco y ventilado.</t>
+  </si>
+  <si>
+    <t>La edad avanzada.</t>
+  </si>
+  <si>
+    <t>¿Qué se debe hacer cuando su vehículo sufre una avería dentro de un túnel?</t>
+  </si>
+  <si>
+    <t>Detener el vehículo en cualquier lugar del túnel para evitar el peligro, aunque la avería permita la circulación del vehículo.</t>
+  </si>
+  <si>
+    <t>Encender las luces de largo alcance para que se vea mejor y hacer que todos los ocupantes bajen del vehículo.</t>
+  </si>
+  <si>
+    <t>Si la avería permite la circulación del vehículo, debe continuar hasta salir del túnel o hasta llegar a una zona reservada para emergencias.</t>
+  </si>
+  <si>
+    <t>En los carriles reservados a bicicletas está prohibido...</t>
+  </si>
+  <si>
+    <t>parar, pero se permite estacionar.</t>
+  </si>
+  <si>
+    <t>estacionar, pero se permite parar.</t>
+  </si>
+  <si>
+    <t>parar y estacionar.</t>
+  </si>
+  <si>
+    <t>¿Por qué será necesario entrar ceñido a la derecha en las curvas hacia la izquierda?</t>
+  </si>
+  <si>
+    <t>Para ampliar la zona de seguridad.</t>
+  </si>
+  <si>
+    <t>Para permitir que los coches que nos preceden puedan adelantar.</t>
+  </si>
+  <si>
+    <t>La pregunta no es correcta ya que deberá entrar ceñido a la izquierda.</t>
+  </si>
+  <si>
+    <t>¿Puede conducir una motocicleta con el permiso de la clase B?</t>
+  </si>
+  <si>
+    <t>Sí, solamente en España, con una cilindrada máxima de 125 centímetros cúbicos, y una antigüedad del permiso superior a tres años.</t>
+  </si>
+  <si>
+    <t>Sí, siempre que sea de una cilindrada menor a 250 centímetros cúbicos.</t>
+  </si>
+  <si>
+    <t>Sí, siempre que no supere los 25 kW de potencia.</t>
+  </si>
+  <si>
+    <t>Ante la lluvia ¿qué debe hacer un conductor por lo que se refiere a la antelación de la frenada?</t>
+  </si>
+  <si>
+    <t>Frenar con menos antelación que en condiciones normales</t>
+  </si>
+  <si>
+    <t>Frenar con la misma antelación que en condiciones normales</t>
+  </si>
+  <si>
+    <t>Frenar con más antelación que en condiciones normales</t>
+  </si>
+  <si>
+    <t>La monotonía y disminución de la atención, es un factor de peligro, que suele presentarse con mayor frecuencia, cuando se circula por...</t>
+  </si>
+  <si>
+    <t>autopista y autovía.</t>
+  </si>
+  <si>
+    <t>vías urbanas y travesías.</t>
+  </si>
+  <si>
+    <t>carreteras convencionales.</t>
+  </si>
+  <si>
+    <t>Si se va a incorporar a una vía utilizando el carril de aceleración, ¿qué deberá comprobar antes de empezar a acelerar para alcanzar una velocidad adecuada a la vía?</t>
+  </si>
+  <si>
+    <t>Que puede incorporarse sin poner en peligro a los usuarios que circulan por la vía.</t>
+  </si>
+  <si>
+    <t>Que los usuarios que circulan por la vía se han dado cuenta de su presencia.</t>
+  </si>
+  <si>
+    <t>Que los usuarios que circulan por la vía lo hacen a velocidad adecuada.</t>
+  </si>
+  <si>
+    <t>La inscripción "BUS" dentro de un carril indica que es...</t>
+  </si>
+  <si>
+    <t>un carril reservado para la circulación de autobuses.</t>
+  </si>
+  <si>
+    <t>un carril destinado al estacionamiento de autobuses.</t>
+  </si>
+  <si>
+    <t>una zona de la vía reservada sólo a turismos y autobuses.</t>
+  </si>
+  <si>
+    <t>En un carril VAO, ¿puede circular un turismo que arrastra un remolque de menos de 750 kg de MMA?</t>
+  </si>
+  <si>
+    <t>Sí, pero solamente de día.</t>
+  </si>
+  <si>
+    <t>Los conos de la fotografía...</t>
+  </si>
+  <si>
+    <t>tienen prioridad sobre el resto de señales.</t>
+  </si>
+  <si>
+    <t>tienen prioridad sobre el resto de señales, salvo las de los agentes de la autoridad.</t>
+  </si>
+  <si>
+    <t>sirven sólo para señalizar un nuevo carril.</t>
+  </si>
+  <si>
+    <t>imagenes/202608195.png</t>
+  </si>
+  <si>
+    <t>¿Cuál es la última fase del adelantamiento?</t>
+  </si>
+  <si>
+    <t>Volver detrás del vehículo al que se pretendía adelantar.</t>
+  </si>
+  <si>
+    <t>El regreso al carril derecho.</t>
+  </si>
+  <si>
+    <t>La aceleración en el carril izquierdo.</t>
+  </si>
+  <si>
+    <t>¿Cuál de éstas luces sirve para cumplir la regla de VER en un vehículo?</t>
+  </si>
+  <si>
+    <t>Luz de corto alcance o cruce</t>
+  </si>
+  <si>
+    <t>Luz de gálibo</t>
+  </si>
+  <si>
+    <t>Fuera de poblado, al acercarnos a un vehículo inmovilizado en la calzada, ¿qué precauciones se deberán tomar?</t>
+  </si>
+  <si>
+    <t>Ninguna, si no vienen vehículos en sentido contrario.</t>
+  </si>
+  <si>
+    <t>Moderar la velocidad, y si es necesario, detener el vehículo.</t>
+  </si>
+  <si>
+    <t>Mantener la velocidad y estar atento para cumplir la señalización vertical.</t>
+  </si>
+  <si>
+    <t>imagenes/202608196.png</t>
+  </si>
+  <si>
+    <t>En esta vía de doble sentido, el conductor del turismo, ¿dónde situará su vehículo para girar a la izquierda?</t>
+  </si>
+  <si>
+    <t>A la derecha, fuera de la calzada siempre que sea posible.</t>
+  </si>
+  <si>
+    <t>Sobre la línea discontinua, invadiendo ligeramente el sentido contrario.</t>
+  </si>
+  <si>
+    <t>Junto a la línea discontinua, sin invadir el sentido contrario.</t>
+  </si>
+  <si>
+    <t>imagenes/202608197.png</t>
+  </si>
+  <si>
+    <t>¿Cuándo puede el conductor de una motocicleta circular sin casco?</t>
+  </si>
+  <si>
+    <t>En cualquier caso ya que el casco es siempre obligatorio.</t>
+  </si>
+  <si>
+    <t>Cuando la motocicleta tiene una estructura de autoprotección y cinturón de seguridad y así aparece en su tarjeta de control técnico.</t>
+  </si>
+  <si>
+    <t>Al viajar por vías urbanas a velocidad reducida.</t>
+  </si>
+  <si>
+    <t>¿Cómo son las luces de posición traseras para las maquinas automotrices agrícolas?</t>
+  </si>
+  <si>
+    <t>Opcionales</t>
+  </si>
+  <si>
+    <t>Innecesarias</t>
+  </si>
+  <si>
+    <t>Obligatorias</t>
+  </si>
+  <si>
+    <t>Circulando entre la puesta y la salida del sol, ¿qué finalidad tiene el sistema ADAS “Asistente de visión nocturna”?</t>
+  </si>
+  <si>
+    <t>Poder desconectar el alumbrado al cruzarse con otro vehículo para evitar el deslumbramiento.</t>
+  </si>
+  <si>
+    <t>Detectar un vehículo inmovilizado fuera de la calzada y de la parte transitable del arcén.</t>
+  </si>
+  <si>
+    <t>Detectar peatones o animales marcándolos en un color u otro en la pantalla de información del conductor.</t>
+  </si>
+  <si>
+    <t>1¿Que indica esta señal de tráfico?</t>
+  </si>
+  <si>
+    <t>La velocidad máxima permitida.</t>
+  </si>
+  <si>
+    <t>La velocidad máxima recomendada.</t>
+  </si>
+  <si>
+    <t>La velocidad mínima recomendada.</t>
+  </si>
+  <si>
+    <t>imagenes/202608198.png</t>
+  </si>
+  <si>
+    <t>En una intersección hay un semáforo en verde y una señal de stop. ¿A cuál se debe obedecer?</t>
+  </si>
+  <si>
+    <t>A ninguna, por ser contradictorias.</t>
+  </si>
+  <si>
+    <t>Al stop, por ser la señal más restrictiva.</t>
+  </si>
+  <si>
+    <t>Al semáforo, por ser la señal prioritaria.</t>
+  </si>
+  <si>
+    <t>¿Cómo debe inmovilizar los vehículos accidentados?</t>
+  </si>
+  <si>
+    <t>Con unos calzos o cualquier elemento que sirva como tal</t>
+  </si>
+  <si>
+    <t>Con el freno de mano y cortando el contacto</t>
+  </si>
+  <si>
+    <t>Quitando el contacto de la batería</t>
+  </si>
+  <si>
+    <t>¿Qué personas incurren en la omisión de socorro a las víctimas de un accidente de tráfico?</t>
+  </si>
+  <si>
+    <t>Las que no ayudan a las víctimas por correr riesgo propio.</t>
+  </si>
+  <si>
+    <t>Las que no socorren a una víctima desatendida, pudiendo hacerlo sin riesgo propio ni de terceros.</t>
+  </si>
+  <si>
+    <t>Las que piden auxilio cuando ellos no pueden prestarlo.</t>
+  </si>
+  <si>
+    <t>¿Se puede invadir totalmente el carril contiguo para adelantar a un peatón fuera de poblado?</t>
+  </si>
+  <si>
+    <t>No, ya que no se puede adelantar a peatones fuera de poblado</t>
+  </si>
+  <si>
+    <t>Sí, si es necesario</t>
+  </si>
+  <si>
+    <t>No, solo se podrá invadir parcialmente</t>
+  </si>
+  <si>
+    <t>En general, bajo los efectos del alcohol los conductores...</t>
+  </si>
+  <si>
+    <t>perciben peor las señales de tráfico.</t>
+  </si>
+  <si>
+    <t>perciben mejor las luces de los semáforos.</t>
+  </si>
+  <si>
+    <t>distinguen mejor las luces de los vehículos.</t>
+  </si>
+  <si>
+    <t>Los principios de la conducción preventiva son...</t>
+  </si>
+  <si>
+    <t>Visión, anticipación y gestión del espacio</t>
+  </si>
+  <si>
+    <t>Rapidez, desconfianza y gestión del espacio.</t>
+  </si>
+  <si>
+    <t>Aceleración, anticipación y desconfianza.</t>
+  </si>
+  <si>
+    <t>Si encuentra esta señal a la entrada de una vía deberás saber que...</t>
+  </si>
+  <si>
+    <t>está prohibida la circulación de ciclomotores.</t>
+  </si>
+  <si>
+    <t>es una vía reservada para ciclos y ciclomotores.</t>
+  </si>
+  <si>
+    <t>está prohibida su utilización para todos aquellos usuarios que no sean conductores de ciclomotores.</t>
+  </si>
+  <si>
+    <t>imagenes/R407b.png</t>
+  </si>
+  <si>
+    <t>¿Cómo es la marca longitudinal continua que delimita un carril especial?</t>
+  </si>
+  <si>
+    <t>Mas ancha que la marca longitudinal continua habitual</t>
+  </si>
+  <si>
+    <t>De color amarillo y rojo</t>
+  </si>
+  <si>
+    <t>Consistente en dos franjas blancas iguales</t>
+  </si>
+  <si>
+    <t>¿Podremos circular a menos de 60 km por hora en una autovía con mucha niebla?</t>
+  </si>
+  <si>
+    <t>Sí, porque con la niebla se debe moderar la velocidad</t>
+  </si>
+  <si>
+    <t>No, porqué es una vía para circulación rápida</t>
+  </si>
+  <si>
+    <t>No, en autovía nunca se debe circular a menos de la velocidad mínima permitida</t>
+  </si>
+  <si>
+    <t>¿Cuál será la velocidad máxima a la que un turismo podrá circular en una autovía?</t>
+  </si>
+  <si>
+    <t>120 km/hora.</t>
+  </si>
+  <si>
+    <t>100 km/hora y hasta 120 km/hora para adelantar.</t>
+  </si>
+  <si>
+    <t>120 km/hora, 140 km/hora para adelantar.</t>
+  </si>
+  <si>
+    <t>¿Es obligatorio que este hombre se ponga un chaleco reflectante?</t>
+  </si>
+  <si>
+    <t>No es obligatorio porqué es de día.</t>
+  </si>
+  <si>
+    <t>Es obligatorio ponerse una pieza de ropa reflectante pero no es necesario que sea un chaleco.</t>
+  </si>
+  <si>
+    <t>Sí, y tiene que ser de alta visibilidad y estar certificado.</t>
+  </si>
+  <si>
+    <t>imagenes/202608199.png</t>
+  </si>
+  <si>
+    <t>28. ¿Pueden los vehículos prioritarios dar marcha atrás en autovía o autopista?</t>
+  </si>
+  <si>
+    <t>Podrán dar marcha atrás pero no media vuelta</t>
+  </si>
+  <si>
+    <t>Sí, con carácter excepcional</t>
+  </si>
+  <si>
+    <t>La conducción preventiva es...</t>
+  </si>
+  <si>
+    <t>una actitud ante la conducción que permite al conductor circular de una manera más segura.</t>
+  </si>
+  <si>
+    <t>una forma de conducción lenta e inadecuada.</t>
+  </si>
+  <si>
+    <t>una forma de conducir peligrosa.</t>
+  </si>
+  <si>
+    <t>¿Está permitido adelantar en los pasos para peatones como norma general? (OJO cambia)</t>
+  </si>
+  <si>
+    <t>No, aunque se podrá adelantar si se hace a una velocidad tan reducida que permita detenerse a tiempo si surgiera un peligro de atropello.</t>
+  </si>
+  <si>
+    <t>Sí, pero sólo en vías urbanas.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2093,9 +2978,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2431,7 +3318,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7778BF-C4D9-8B46-A8CD-4B3F292AD9D0}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:F231"/>
+  <dimension ref="A1:F271"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.5" bestFit="1" customWidth="1"/>
@@ -3063,13 +3950,13 @@
         <v>151</v>
       </c>
       <c r="B32" t="s">
-        <v>509</v>
+        <v>477</v>
       </c>
       <c r="C32" t="s">
-        <v>564</v>
+        <v>532</v>
       </c>
       <c r="D32" t="s">
-        <v>619</v>
+        <v>587</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
@@ -3083,13 +3970,13 @@
         <v>153</v>
       </c>
       <c r="B33" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="C33" t="s">
-        <v>565</v>
+        <v>533</v>
       </c>
       <c r="D33" t="s">
-        <v>620</v>
+        <v>588</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -3100,102 +3987,102 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>665</v>
       </c>
       <c r="B34" t="s">
-        <v>511</v>
+        <v>479</v>
       </c>
       <c r="C34" t="s">
-        <v>566</v>
+        <v>534</v>
       </c>
       <c r="D34" t="s">
-        <v>621</v>
+        <v>589</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" t="s">
+        <v>480</v>
+      </c>
+      <c r="C35" t="s">
+        <v>535</v>
+      </c>
+      <c r="D35" t="s">
+        <v>590</v>
+      </c>
+      <c r="E35" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" t="s">
         <v>157</v>
-      </c>
-      <c r="B35" t="s">
-        <v>512</v>
-      </c>
-      <c r="C35" t="s">
-        <v>567</v>
-      </c>
-      <c r="D35" t="s">
-        <v>622</v>
-      </c>
-      <c r="E35" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" t="s">
+        <v>481</v>
+      </c>
+      <c r="C36" t="s">
+        <v>536</v>
+      </c>
+      <c r="D36" t="s">
+        <v>591</v>
+      </c>
+      <c r="E36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" t="s">
         <v>159</v>
-      </c>
-      <c r="B36" t="s">
-        <v>513</v>
-      </c>
-      <c r="C36" t="s">
-        <v>568</v>
-      </c>
-      <c r="D36" t="s">
-        <v>623</v>
-      </c>
-      <c r="E36" t="s">
-        <v>17</v>
-      </c>
-      <c r="F36" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" t="s">
+        <v>482</v>
+      </c>
+      <c r="C37" t="s">
+        <v>537</v>
+      </c>
+      <c r="D37" t="s">
+        <v>592</v>
+      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" t="s">
         <v>161</v>
-      </c>
-      <c r="B37" t="s">
-        <v>514</v>
-      </c>
-      <c r="C37" t="s">
-        <v>569</v>
-      </c>
-      <c r="D37" t="s">
-        <v>624</v>
-      </c>
-      <c r="E37" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" t="s">
+        <v>483</v>
+      </c>
+      <c r="C38" t="s">
+        <v>538</v>
+      </c>
+      <c r="D38" t="s">
+        <v>593</v>
+      </c>
+      <c r="E38" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" t="s">
         <v>163</v>
-      </c>
-      <c r="B38" t="s">
-        <v>515</v>
-      </c>
-      <c r="C38" t="s">
-        <v>570</v>
-      </c>
-      <c r="D38" t="s">
-        <v>625</v>
-      </c>
-      <c r="E38" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -3203,110 +4090,110 @@
         <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>516</v>
+        <v>484</v>
       </c>
       <c r="C39" t="s">
-        <v>571</v>
+        <v>539</v>
       </c>
       <c r="D39" t="s">
-        <v>626</v>
+        <v>594</v>
       </c>
       <c r="E39" t="s">
         <v>7</v>
       </c>
       <c r="F39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B40" t="s">
+        <v>485</v>
+      </c>
+      <c r="C40" t="s">
+        <v>540</v>
+      </c>
+      <c r="D40" t="s">
+        <v>595</v>
+      </c>
+      <c r="E40" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" t="s">
         <v>166</v>
-      </c>
-      <c r="B40" t="s">
-        <v>517</v>
-      </c>
-      <c r="C40" t="s">
-        <v>572</v>
-      </c>
-      <c r="D40" t="s">
-        <v>627</v>
-      </c>
-      <c r="E40" t="s">
-        <v>17</v>
-      </c>
-      <c r="F40" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41" t="s">
+        <v>486</v>
+      </c>
+      <c r="C41" t="s">
+        <v>541</v>
+      </c>
+      <c r="D41" t="s">
+        <v>596</v>
+      </c>
+      <c r="E41" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" t="s">
         <v>168</v>
-      </c>
-      <c r="B41" t="s">
-        <v>518</v>
-      </c>
-      <c r="C41" t="s">
-        <v>573</v>
-      </c>
-      <c r="D41" t="s">
-        <v>628</v>
-      </c>
-      <c r="E41" t="s">
-        <v>17</v>
-      </c>
-      <c r="F41" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B42" t="s">
         <v>82</v>
       </c>
       <c r="C42" t="s">
-        <v>574</v>
+        <v>542</v>
       </c>
       <c r="D42" t="s">
-        <v>629</v>
+        <v>597</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B43" t="s">
-        <v>519</v>
+        <v>487</v>
       </c>
       <c r="C43" t="s">
-        <v>575</v>
+        <v>543</v>
       </c>
       <c r="D43" t="s">
-        <v>630</v>
+        <v>598</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B44" t="s">
-        <v>520</v>
+        <v>488</v>
       </c>
       <c r="C44" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
       <c r="D44" t="s">
         <v>82</v>
@@ -3315,361 +4202,361 @@
         <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>175</v>
+      </c>
+      <c r="B45" t="s">
+        <v>489</v>
+      </c>
+      <c r="C45" t="s">
+        <v>545</v>
+      </c>
+      <c r="D45" t="s">
+        <v>599</v>
+      </c>
+      <c r="E45" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" t="s">
         <v>176</v>
-      </c>
-      <c r="B45" t="s">
-        <v>521</v>
-      </c>
-      <c r="C45" t="s">
-        <v>577</v>
-      </c>
-      <c r="D45" t="s">
-        <v>631</v>
-      </c>
-      <c r="E45" t="s">
-        <v>17</v>
-      </c>
-      <c r="F45" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B46" t="s">
-        <v>522</v>
+        <v>490</v>
       </c>
       <c r="C46" t="s">
-        <v>578</v>
+        <v>546</v>
       </c>
       <c r="D46" t="s">
-        <v>632</v>
+        <v>600</v>
       </c>
       <c r="E46" t="s">
         <v>7</v>
       </c>
       <c r="F46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>179</v>
+      </c>
+      <c r="B47" t="s">
+        <v>491</v>
+      </c>
+      <c r="C47" t="s">
+        <v>547</v>
+      </c>
+      <c r="D47" t="s">
+        <v>601</v>
+      </c>
+      <c r="E47" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" t="s">
         <v>180</v>
-      </c>
-      <c r="B47" t="s">
-        <v>523</v>
-      </c>
-      <c r="C47" t="s">
-        <v>579</v>
-      </c>
-      <c r="D47" t="s">
-        <v>633</v>
-      </c>
-      <c r="E47" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B48" t="s">
-        <v>524</v>
+        <v>492</v>
       </c>
       <c r="C48" t="s">
         <v>71</v>
       </c>
       <c r="D48" t="s">
-        <v>634</v>
+        <v>602</v>
       </c>
       <c r="E48" t="s">
         <v>7</v>
       </c>
       <c r="F48" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B49" t="s">
-        <v>525</v>
+        <v>493</v>
       </c>
       <c r="C49" t="s">
-        <v>580</v>
+        <v>548</v>
       </c>
       <c r="D49" t="s">
-        <v>635</v>
+        <v>603</v>
       </c>
       <c r="E49" t="s">
         <v>7</v>
       </c>
       <c r="F49" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B50" t="s">
-        <v>526</v>
+        <v>494</v>
       </c>
       <c r="C50" t="s">
         <v>82</v>
       </c>
       <c r="D50" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="E50" t="s">
         <v>7</v>
       </c>
       <c r="F50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" t="s">
+        <v>495</v>
+      </c>
+      <c r="C51" t="s">
+        <v>549</v>
+      </c>
+      <c r="D51" t="s">
+        <v>427</v>
+      </c>
+      <c r="E51" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" t="s">
         <v>188</v>
-      </c>
-      <c r="B51" t="s">
-        <v>527</v>
-      </c>
-      <c r="C51" t="s">
-        <v>581</v>
-      </c>
-      <c r="D51" t="s">
-        <v>429</v>
-      </c>
-      <c r="E51" t="s">
-        <v>17</v>
-      </c>
-      <c r="F51" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B52" t="s">
-        <v>528</v>
+        <v>496</v>
       </c>
       <c r="C52" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="D52" t="s">
-        <v>637</v>
+        <v>605</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>191</v>
+      </c>
+      <c r="B53" t="s">
+        <v>497</v>
+      </c>
+      <c r="C53" t="s">
+        <v>551</v>
+      </c>
+      <c r="D53" t="s">
+        <v>606</v>
+      </c>
+      <c r="E53" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" t="s">
         <v>192</v>
-      </c>
-      <c r="B53" t="s">
-        <v>529</v>
-      </c>
-      <c r="C53" t="s">
-        <v>583</v>
-      </c>
-      <c r="D53" t="s">
-        <v>638</v>
-      </c>
-      <c r="E53" t="s">
-        <v>17</v>
-      </c>
-      <c r="F53" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B54" t="s">
-        <v>530</v>
+        <v>498</v>
       </c>
       <c r="C54" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="D54" t="s">
-        <v>639</v>
+        <v>607</v>
       </c>
       <c r="E54" t="s">
         <v>7</v>
       </c>
       <c r="F54" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>196</v>
+        <v>645</v>
       </c>
       <c r="B55" t="s">
-        <v>531</v>
+        <v>499</v>
       </c>
       <c r="C55" t="s">
-        <v>585</v>
+        <v>553</v>
       </c>
       <c r="D55" t="s">
-        <v>640</v>
+        <v>608</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B56" t="s">
-        <v>532</v>
+        <v>500</v>
       </c>
       <c r="C56" t="s">
-        <v>586</v>
+        <v>554</v>
       </c>
       <c r="D56" t="s">
-        <v>641</v>
+        <v>609</v>
       </c>
       <c r="E56" t="s">
         <v>7</v>
       </c>
       <c r="F56" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B57" t="s">
-        <v>533</v>
+        <v>501</v>
       </c>
       <c r="C57" t="s">
-        <v>587</v>
+        <v>555</v>
       </c>
       <c r="D57" t="s">
-        <v>642</v>
+        <v>610</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B58" t="s">
-        <v>534</v>
+        <v>502</v>
       </c>
       <c r="C58" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="D58" t="s">
-        <v>643</v>
+        <v>611</v>
       </c>
       <c r="E58" t="s">
         <v>17</v>
       </c>
       <c r="F58" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B59" t="s">
-        <v>535</v>
+        <v>503</v>
       </c>
       <c r="C59" t="s">
-        <v>589</v>
+        <v>557</v>
       </c>
       <c r="D59" t="s">
-        <v>644</v>
+        <v>612</v>
       </c>
       <c r="E59" t="s">
         <v>7</v>
       </c>
       <c r="F59" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B60" t="s">
-        <v>536</v>
+        <v>504</v>
       </c>
       <c r="C60" t="s">
-        <v>590</v>
+        <v>558</v>
       </c>
       <c r="D60" t="s">
-        <v>645</v>
+        <v>613</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
       </c>
       <c r="F60" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B61" t="s">
-        <v>537</v>
+        <v>505</v>
       </c>
       <c r="C61" t="s">
-        <v>591</v>
+        <v>559</v>
       </c>
       <c r="D61" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E61" t="s">
         <v>7</v>
       </c>
       <c r="F61" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>208</v>
+      </c>
+      <c r="B62" t="s">
+        <v>209</v>
+      </c>
+      <c r="C62" t="s">
         <v>210</v>
       </c>
-      <c r="B62" t="s">
+      <c r="D62" t="s">
         <v>211</v>
-      </c>
-      <c r="C62" t="s">
-        <v>212</v>
-      </c>
-      <c r="D62" t="s">
-        <v>213</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -3677,16 +4564,16 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>212</v>
+      </c>
+      <c r="B63" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" t="s">
         <v>214</v>
       </c>
-      <c r="B63" t="s">
+      <c r="D63" t="s">
         <v>215</v>
-      </c>
-      <c r="C63" t="s">
-        <v>216</v>
-      </c>
-      <c r="D63" t="s">
-        <v>217</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
@@ -3694,16 +4581,16 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>216</v>
+      </c>
+      <c r="B64" t="s">
+        <v>217</v>
+      </c>
+      <c r="C64" t="s">
         <v>218</v>
       </c>
-      <c r="B64" t="s">
+      <c r="D64" t="s">
         <v>219</v>
-      </c>
-      <c r="C64" t="s">
-        <v>220</v>
-      </c>
-      <c r="D64" t="s">
-        <v>221</v>
       </c>
       <c r="E64" t="s">
         <v>7</v>
@@ -3711,22 +4598,22 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>220</v>
+      </c>
+      <c r="B65" t="s">
+        <v>221</v>
+      </c>
+      <c r="C65" t="s">
         <v>222</v>
       </c>
-      <c r="B65" t="s">
+      <c r="D65" t="s">
         <v>223</v>
       </c>
-      <c r="C65" t="s">
+      <c r="E65" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" t="s">
         <v>224</v>
-      </c>
-      <c r="D65" t="s">
-        <v>225</v>
-      </c>
-      <c r="E65" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
@@ -3734,33 +4621,33 @@
         <v>33</v>
       </c>
       <c r="B66" t="s">
+        <v>225</v>
+      </c>
+      <c r="C66" t="s">
+        <v>226</v>
+      </c>
+      <c r="D66" t="s">
         <v>227</v>
       </c>
-      <c r="C66" t="s">
+      <c r="E66" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" t="s">
         <v>228</v>
-      </c>
-      <c r="D66" t="s">
-        <v>229</v>
-      </c>
-      <c r="E66" t="s">
-        <v>17</v>
-      </c>
-      <c r="F66" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
+        <v>229</v>
+      </c>
+      <c r="B67" t="s">
+        <v>230</v>
+      </c>
+      <c r="C67" t="s">
         <v>231</v>
       </c>
-      <c r="B67" t="s">
+      <c r="D67" t="s">
         <v>232</v>
-      </c>
-      <c r="C67" t="s">
-        <v>233</v>
-      </c>
-      <c r="D67" t="s">
-        <v>234</v>
       </c>
       <c r="E67" t="s">
         <v>7</v>
@@ -3768,36 +4655,36 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>233</v>
+      </c>
+      <c r="B68" t="s">
+        <v>234</v>
+      </c>
+      <c r="C68" t="s">
         <v>235</v>
       </c>
-      <c r="B68" t="s">
+      <c r="D68" t="s">
         <v>236</v>
-      </c>
-      <c r="C68" t="s">
-        <v>237</v>
-      </c>
-      <c r="D68" t="s">
-        <v>238</v>
       </c>
       <c r="E68" t="s">
         <v>7</v>
       </c>
       <c r="F68" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>238</v>
+      </c>
+      <c r="B69" t="s">
+        <v>239</v>
+      </c>
+      <c r="C69" t="s">
         <v>240</v>
       </c>
-      <c r="B69" t="s">
+      <c r="D69" t="s">
         <v>241</v>
-      </c>
-      <c r="C69" t="s">
-        <v>242</v>
-      </c>
-      <c r="D69" t="s">
-        <v>243</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
@@ -3805,36 +4692,36 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>242</v>
+      </c>
+      <c r="B70" t="s">
+        <v>243</v>
+      </c>
+      <c r="C70" t="s">
         <v>244</v>
       </c>
-      <c r="B70" t="s">
+      <c r="D70" t="s">
         <v>245</v>
-      </c>
-      <c r="C70" t="s">
-        <v>246</v>
-      </c>
-      <c r="D70" t="s">
-        <v>247</v>
       </c>
       <c r="E70" t="s">
         <v>7</v>
       </c>
       <c r="F70" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>247</v>
+      </c>
+      <c r="B71" t="s">
+        <v>248</v>
+      </c>
+      <c r="C71" t="s">
         <v>249</v>
       </c>
-      <c r="B71" t="s">
+      <c r="D71" t="s">
         <v>250</v>
-      </c>
-      <c r="C71" t="s">
-        <v>251</v>
-      </c>
-      <c r="D71" t="s">
-        <v>252</v>
       </c>
       <c r="E71" t="s">
         <v>17</v>
@@ -3842,16 +4729,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>251</v>
+      </c>
+      <c r="B72" t="s">
+        <v>252</v>
+      </c>
+      <c r="C72" t="s">
         <v>253</v>
       </c>
-      <c r="B72" t="s">
+      <c r="D72" t="s">
         <v>254</v>
-      </c>
-      <c r="C72" t="s">
-        <v>255</v>
-      </c>
-      <c r="D72" t="s">
-        <v>256</v>
       </c>
       <c r="E72" t="s">
         <v>17</v>
@@ -3859,56 +4746,56 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>255</v>
+      </c>
+      <c r="B73" t="s">
+        <v>256</v>
+      </c>
+      <c r="C73" t="s">
         <v>257</v>
       </c>
-      <c r="B73" t="s">
+      <c r="D73" t="s">
         <v>258</v>
-      </c>
-      <c r="C73" t="s">
-        <v>259</v>
-      </c>
-      <c r="D73" t="s">
-        <v>260</v>
       </c>
       <c r="E73" t="s">
         <v>7</v>
       </c>
       <c r="F73" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>260</v>
+      </c>
+      <c r="B74" t="s">
+        <v>261</v>
+      </c>
+      <c r="C74" t="s">
         <v>262</v>
       </c>
-      <c r="B74" t="s">
+      <c r="D74" t="s">
         <v>263</v>
       </c>
-      <c r="C74" t="s">
+      <c r="E74" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" t="s">
         <v>264</v>
-      </c>
-      <c r="D74" t="s">
-        <v>265</v>
-      </c>
-      <c r="E74" t="s">
-        <v>17</v>
-      </c>
-      <c r="F74" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>265</v>
+      </c>
+      <c r="B75" t="s">
+        <v>266</v>
+      </c>
+      <c r="C75" t="s">
         <v>267</v>
       </c>
-      <c r="B75" t="s">
+      <c r="D75" t="s">
         <v>268</v>
-      </c>
-      <c r="C75" t="s">
-        <v>269</v>
-      </c>
-      <c r="D75" t="s">
-        <v>270</v>
       </c>
       <c r="E75" t="s">
         <v>7</v>
@@ -3916,16 +4803,16 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
+        <v>269</v>
+      </c>
+      <c r="B76" t="s">
+        <v>270</v>
+      </c>
+      <c r="C76" t="s">
         <v>271</v>
       </c>
-      <c r="B76" t="s">
+      <c r="D76" t="s">
         <v>272</v>
-      </c>
-      <c r="C76" t="s">
-        <v>273</v>
-      </c>
-      <c r="D76" t="s">
-        <v>274</v>
       </c>
       <c r="E76" t="s">
         <v>10</v>
@@ -3933,16 +4820,16 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
+        <v>273</v>
+      </c>
+      <c r="B77" t="s">
+        <v>210</v>
+      </c>
+      <c r="C77" t="s">
+        <v>274</v>
+      </c>
+      <c r="D77" t="s">
         <v>275</v>
-      </c>
-      <c r="B77" t="s">
-        <v>212</v>
-      </c>
-      <c r="C77" t="s">
-        <v>276</v>
-      </c>
-      <c r="D77" t="s">
-        <v>277</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
@@ -3950,96 +4837,96 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>276</v>
+      </c>
+      <c r="B78" t="s">
+        <v>277</v>
+      </c>
+      <c r="C78" t="s">
         <v>278</v>
       </c>
-      <c r="B78" t="s">
+      <c r="D78" t="s">
         <v>279</v>
-      </c>
-      <c r="C78" t="s">
-        <v>280</v>
-      </c>
-      <c r="D78" t="s">
-        <v>281</v>
       </c>
       <c r="E78" t="s">
         <v>7</v>
       </c>
       <c r="F78" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
+        <v>281</v>
+      </c>
+      <c r="B79" t="s">
+        <v>282</v>
+      </c>
+      <c r="C79" t="s">
         <v>283</v>
       </c>
-      <c r="B79" t="s">
+      <c r="D79" t="s">
         <v>284</v>
-      </c>
-      <c r="C79" t="s">
-        <v>285</v>
-      </c>
-      <c r="D79" t="s">
-        <v>286</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
       </c>
       <c r="F79" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>286</v>
+      </c>
+      <c r="B80" t="s">
+        <v>287</v>
+      </c>
+      <c r="C80" t="s">
         <v>288</v>
       </c>
-      <c r="B80" t="s">
+      <c r="D80" t="s">
         <v>289</v>
-      </c>
-      <c r="C80" t="s">
-        <v>290</v>
-      </c>
-      <c r="D80" t="s">
-        <v>291</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
+        <v>291</v>
+      </c>
+      <c r="B81" t="s">
+        <v>292</v>
+      </c>
+      <c r="C81" t="s">
         <v>293</v>
       </c>
-      <c r="B81" t="s">
+      <c r="D81" t="s">
+        <v>210</v>
+      </c>
+      <c r="E81" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" t="s">
         <v>294</v>
-      </c>
-      <c r="C81" t="s">
-        <v>295</v>
-      </c>
-      <c r="D81" t="s">
-        <v>212</v>
-      </c>
-      <c r="E81" t="s">
-        <v>17</v>
-      </c>
-      <c r="F81" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>295</v>
+      </c>
+      <c r="B82" t="s">
+        <v>296</v>
+      </c>
+      <c r="C82" t="s">
         <v>297</v>
       </c>
-      <c r="B82" t="s">
+      <c r="D82" t="s">
         <v>298</v>
-      </c>
-      <c r="C82" t="s">
-        <v>299</v>
-      </c>
-      <c r="D82" t="s">
-        <v>300</v>
       </c>
       <c r="E82" t="s">
         <v>17</v>
@@ -4047,116 +4934,116 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>299</v>
+      </c>
+      <c r="B83" t="s">
+        <v>300</v>
+      </c>
+      <c r="C83" t="s">
         <v>301</v>
       </c>
-      <c r="B83" t="s">
+      <c r="D83" t="s">
         <v>302</v>
-      </c>
-      <c r="C83" t="s">
-        <v>303</v>
-      </c>
-      <c r="D83" t="s">
-        <v>304</v>
       </c>
       <c r="E83" t="s">
         <v>7</v>
       </c>
       <c r="F83" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
+        <v>304</v>
+      </c>
+      <c r="B84" t="s">
+        <v>305</v>
+      </c>
+      <c r="C84" t="s">
         <v>306</v>
       </c>
-      <c r="B84" t="s">
+      <c r="D84" t="s">
         <v>307</v>
       </c>
-      <c r="C84" t="s">
+      <c r="E84" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" t="s">
         <v>308</v>
-      </c>
-      <c r="D84" t="s">
-        <v>309</v>
-      </c>
-      <c r="E84" t="s">
-        <v>17</v>
-      </c>
-      <c r="F84" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
+        <v>309</v>
+      </c>
+      <c r="B85" t="s">
+        <v>310</v>
+      </c>
+      <c r="C85" t="s">
         <v>311</v>
       </c>
-      <c r="B85" t="s">
+      <c r="D85" t="s">
         <v>312</v>
       </c>
-      <c r="C85" t="s">
+      <c r="E85" t="s">
+        <v>17</v>
+      </c>
+      <c r="F85" t="s">
         <v>313</v>
-      </c>
-      <c r="D85" t="s">
-        <v>314</v>
-      </c>
-      <c r="E85" t="s">
-        <v>17</v>
-      </c>
-      <c r="F85" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
+        <v>314</v>
+      </c>
+      <c r="B86" t="s">
+        <v>315</v>
+      </c>
+      <c r="C86" t="s">
         <v>316</v>
       </c>
-      <c r="B86" t="s">
+      <c r="D86" t="s">
         <v>317</v>
       </c>
-      <c r="C86" t="s">
+      <c r="E86" t="s">
+        <v>17</v>
+      </c>
+      <c r="F86" t="s">
         <v>318</v>
-      </c>
-      <c r="D86" t="s">
-        <v>319</v>
-      </c>
-      <c r="E86" t="s">
-        <v>17</v>
-      </c>
-      <c r="F86" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>319</v>
+      </c>
+      <c r="B87" t="s">
+        <v>320</v>
+      </c>
+      <c r="C87" t="s">
         <v>321</v>
       </c>
-      <c r="B87" t="s">
+      <c r="D87" t="s">
         <v>322</v>
-      </c>
-      <c r="C87" t="s">
-        <v>323</v>
-      </c>
-      <c r="D87" t="s">
-        <v>324</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
       </c>
       <c r="F87" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
+        <v>324</v>
+      </c>
+      <c r="B88" t="s">
+        <v>325</v>
+      </c>
+      <c r="C88" t="s">
         <v>326</v>
       </c>
-      <c r="B88" t="s">
+      <c r="D88" t="s">
         <v>327</v>
-      </c>
-      <c r="C88" t="s">
-        <v>328</v>
-      </c>
-      <c r="D88" t="s">
-        <v>329</v>
       </c>
       <c r="E88" t="s">
         <v>7</v>
@@ -4164,76 +5051,76 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>328</v>
+      </c>
+      <c r="B89" t="s">
+        <v>329</v>
+      </c>
+      <c r="C89" t="s">
         <v>330</v>
       </c>
-      <c r="B89" t="s">
+      <c r="D89" t="s">
         <v>331</v>
-      </c>
-      <c r="C89" t="s">
-        <v>332</v>
-      </c>
-      <c r="D89" t="s">
-        <v>333</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
       </c>
       <c r="F89" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
+        <v>333</v>
+      </c>
+      <c r="B90" t="s">
+        <v>334</v>
+      </c>
+      <c r="C90" t="s">
         <v>335</v>
       </c>
-      <c r="B90" t="s">
+      <c r="D90" t="s">
         <v>336</v>
       </c>
-      <c r="C90" t="s">
+      <c r="E90" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" t="s">
         <v>337</v>
-      </c>
-      <c r="D90" t="s">
-        <v>338</v>
-      </c>
-      <c r="E90" t="s">
-        <v>17</v>
-      </c>
-      <c r="F90" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>338</v>
+      </c>
+      <c r="B91" t="s">
+        <v>339</v>
+      </c>
+      <c r="C91" t="s">
         <v>340</v>
       </c>
-      <c r="B91" t="s">
+      <c r="D91" t="s">
         <v>341</v>
       </c>
-      <c r="C91" t="s">
+      <c r="E91" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91" t="s">
         <v>342</v>
-      </c>
-      <c r="D91" t="s">
-        <v>343</v>
-      </c>
-      <c r="E91" t="s">
-        <v>17</v>
-      </c>
-      <c r="F91" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>343</v>
+      </c>
+      <c r="B92" t="s">
+        <v>344</v>
+      </c>
+      <c r="C92" t="s">
         <v>345</v>
       </c>
-      <c r="B92" t="s">
+      <c r="D92" t="s">
         <v>346</v>
-      </c>
-      <c r="C92" t="s">
-        <v>347</v>
-      </c>
-      <c r="D92" t="s">
-        <v>348</v>
       </c>
       <c r="E92" t="s">
         <v>17</v>
@@ -4241,16 +5128,16 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
+        <v>347</v>
+      </c>
+      <c r="B93" t="s">
+        <v>348</v>
+      </c>
+      <c r="C93" t="s">
         <v>349</v>
       </c>
-      <c r="B93" t="s">
+      <c r="D93" t="s">
         <v>350</v>
-      </c>
-      <c r="C93" t="s">
-        <v>351</v>
-      </c>
-      <c r="D93" t="s">
-        <v>352</v>
       </c>
       <c r="E93" t="s">
         <v>7</v>
@@ -4258,16 +5145,16 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>351</v>
+      </c>
+      <c r="B94" t="s">
+        <v>352</v>
+      </c>
+      <c r="C94" t="s">
         <v>353</v>
       </c>
-      <c r="B94" t="s">
+      <c r="D94" t="s">
         <v>354</v>
-      </c>
-      <c r="C94" t="s">
-        <v>355</v>
-      </c>
-      <c r="D94" t="s">
-        <v>356</v>
       </c>
       <c r="E94" t="s">
         <v>7</v>
@@ -4275,13 +5162,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
+        <v>355</v>
+      </c>
+      <c r="B95" t="s">
+        <v>356</v>
+      </c>
+      <c r="C95" t="s">
         <v>357</v>
-      </c>
-      <c r="B95" t="s">
-        <v>358</v>
-      </c>
-      <c r="C95" t="s">
-        <v>359</v>
       </c>
       <c r="D95" t="s">
         <v>82</v>
@@ -4292,16 +5179,16 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B96" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C96" t="s">
         <v>82</v>
       </c>
       <c r="D96" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
@@ -4309,76 +5196,76 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
+        <v>361</v>
+      </c>
+      <c r="B97" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" t="s">
         <v>363</v>
       </c>
-      <c r="B97" t="s">
+      <c r="D97" t="s">
         <v>364</v>
-      </c>
-      <c r="C97" t="s">
-        <v>365</v>
-      </c>
-      <c r="D97" t="s">
-        <v>366</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>366</v>
+      </c>
+      <c r="B98" t="s">
+        <v>367</v>
+      </c>
+      <c r="C98" t="s">
         <v>368</v>
       </c>
-      <c r="B98" t="s">
+      <c r="D98" t="s">
         <v>369</v>
-      </c>
-      <c r="C98" t="s">
-        <v>370</v>
-      </c>
-      <c r="D98" t="s">
-        <v>371</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
       </c>
       <c r="F98" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>371</v>
+      </c>
+      <c r="B99" t="s">
+        <v>372</v>
+      </c>
+      <c r="C99" t="s">
         <v>373</v>
       </c>
-      <c r="B99" t="s">
+      <c r="D99" t="s">
         <v>374</v>
-      </c>
-      <c r="C99" t="s">
-        <v>375</v>
-      </c>
-      <c r="D99" t="s">
-        <v>376</v>
       </c>
       <c r="E99" t="s">
         <v>10</v>
       </c>
       <c r="F99" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>376</v>
+      </c>
+      <c r="B100" t="s">
+        <v>377</v>
+      </c>
+      <c r="C100" t="s">
         <v>378</v>
       </c>
-      <c r="B100" t="s">
+      <c r="D100" t="s">
         <v>379</v>
-      </c>
-      <c r="C100" t="s">
-        <v>380</v>
-      </c>
-      <c r="D100" t="s">
-        <v>381</v>
       </c>
       <c r="E100" t="s">
         <v>10</v>
@@ -4386,16 +5273,16 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>380</v>
+      </c>
+      <c r="B101" t="s">
+        <v>381</v>
+      </c>
+      <c r="C101" t="s">
         <v>382</v>
       </c>
-      <c r="B101" t="s">
+      <c r="D101" t="s">
         <v>383</v>
-      </c>
-      <c r="C101" t="s">
-        <v>384</v>
-      </c>
-      <c r="D101" t="s">
-        <v>385</v>
       </c>
       <c r="E101" t="s">
         <v>17</v>
@@ -4403,10 +5290,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B102" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C102" t="s">
         <v>71</v>
@@ -4418,41 +5305,41 @@
         <v>7</v>
       </c>
       <c r="F102" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>387</v>
+      </c>
+      <c r="B103" t="s">
+        <v>388</v>
+      </c>
+      <c r="C103" t="s">
         <v>389</v>
       </c>
-      <c r="B103" t="s">
+      <c r="D103" t="s">
         <v>390</v>
       </c>
-      <c r="C103" t="s">
+      <c r="E103" t="s">
+        <v>17</v>
+      </c>
+      <c r="F103" t="s">
         <v>391</v>
-      </c>
-      <c r="D103" t="s">
-        <v>392</v>
-      </c>
-      <c r="E103" t="s">
-        <v>17</v>
-      </c>
-      <c r="F103" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
+        <v>392</v>
+      </c>
+      <c r="B104" t="s">
+        <v>393</v>
+      </c>
+      <c r="C104" t="s">
         <v>394</v>
       </c>
-      <c r="B104" t="s">
+      <c r="D104" t="s">
         <v>395</v>
-      </c>
-      <c r="C104" t="s">
-        <v>396</v>
-      </c>
-      <c r="D104" t="s">
-        <v>397</v>
       </c>
       <c r="E104" t="s">
         <v>7</v>
@@ -4460,16 +5347,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
+        <v>396</v>
+      </c>
+      <c r="B105" t="s">
+        <v>397</v>
+      </c>
+      <c r="C105" t="s">
         <v>398</v>
       </c>
-      <c r="B105" t="s">
+      <c r="D105" t="s">
         <v>399</v>
-      </c>
-      <c r="C105" t="s">
-        <v>400</v>
-      </c>
-      <c r="D105" t="s">
-        <v>401</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
@@ -4477,16 +5364,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
+        <v>400</v>
+      </c>
+      <c r="B106" t="s">
+        <v>401</v>
+      </c>
+      <c r="C106" t="s">
         <v>402</v>
       </c>
-      <c r="B106" t="s">
+      <c r="D106" t="s">
         <v>403</v>
-      </c>
-      <c r="C106" t="s">
-        <v>404</v>
-      </c>
-      <c r="D106" t="s">
-        <v>405</v>
       </c>
       <c r="E106" t="s">
         <v>17</v>
@@ -4494,16 +5381,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
+        <v>404</v>
+      </c>
+      <c r="B107" t="s">
+        <v>405</v>
+      </c>
+      <c r="C107" t="s">
         <v>406</v>
       </c>
-      <c r="B107" t="s">
+      <c r="D107" t="s">
         <v>407</v>
-      </c>
-      <c r="C107" t="s">
-        <v>408</v>
-      </c>
-      <c r="D107" t="s">
-        <v>409</v>
       </c>
       <c r="E107" t="s">
         <v>10</v>
@@ -4511,16 +5398,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
+        <v>408</v>
+      </c>
+      <c r="B108" t="s">
+        <v>409</v>
+      </c>
+      <c r="C108" t="s">
         <v>410</v>
       </c>
-      <c r="B108" t="s">
+      <c r="D108" t="s">
         <v>411</v>
-      </c>
-      <c r="C108" t="s">
-        <v>412</v>
-      </c>
-      <c r="D108" t="s">
-        <v>413</v>
       </c>
       <c r="E108" t="s">
         <v>7</v>
@@ -4528,36 +5415,36 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
+        <v>412</v>
+      </c>
+      <c r="B109" t="s">
+        <v>382</v>
+      </c>
+      <c r="C109" t="s">
+        <v>413</v>
+      </c>
+      <c r="D109" t="s">
         <v>414</v>
-      </c>
-      <c r="B109" t="s">
-        <v>384</v>
-      </c>
-      <c r="C109" t="s">
-        <v>415</v>
-      </c>
-      <c r="D109" t="s">
-        <v>416</v>
       </c>
       <c r="E109" t="s">
         <v>10</v>
       </c>
       <c r="F109" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
+        <v>416</v>
+      </c>
+      <c r="B110" t="s">
+        <v>417</v>
+      </c>
+      <c r="C110" t="s">
         <v>418</v>
       </c>
-      <c r="B110" t="s">
+      <c r="D110" t="s">
         <v>419</v>
-      </c>
-      <c r="C110" t="s">
-        <v>420</v>
-      </c>
-      <c r="D110" t="s">
-        <v>421</v>
       </c>
       <c r="E110" t="s">
         <v>10</v>
@@ -4565,16 +5452,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
+        <v>420</v>
+      </c>
+      <c r="B111" t="s">
+        <v>421</v>
+      </c>
+      <c r="C111" t="s">
         <v>422</v>
       </c>
-      <c r="B111" t="s">
+      <c r="D111" t="s">
         <v>423</v>
-      </c>
-      <c r="C111" t="s">
-        <v>424</v>
-      </c>
-      <c r="D111" t="s">
-        <v>425</v>
       </c>
       <c r="E111" t="s">
         <v>7</v>
@@ -4582,56 +5469,56 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
+        <v>424</v>
+      </c>
+      <c r="B112" t="s">
+        <v>425</v>
+      </c>
+      <c r="C112" t="s">
         <v>426</v>
       </c>
-      <c r="B112" t="s">
+      <c r="D112" t="s">
         <v>427</v>
-      </c>
-      <c r="C112" t="s">
-        <v>428</v>
-      </c>
-      <c r="D112" t="s">
-        <v>429</v>
       </c>
       <c r="E112" t="s">
         <v>7</v>
       </c>
       <c r="F112" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>429</v>
+      </c>
+      <c r="B113" t="s">
+        <v>430</v>
+      </c>
+      <c r="C113" t="s">
         <v>431</v>
       </c>
-      <c r="B113" t="s">
+      <c r="D113" t="s">
+        <v>278</v>
+      </c>
+      <c r="E113" t="s">
+        <v>17</v>
+      </c>
+      <c r="F113" t="s">
         <v>432</v>
-      </c>
-      <c r="C113" t="s">
-        <v>433</v>
-      </c>
-      <c r="D113" t="s">
-        <v>280</v>
-      </c>
-      <c r="E113" t="s">
-        <v>17</v>
-      </c>
-      <c r="F113" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
+        <v>433</v>
+      </c>
+      <c r="B114" t="s">
+        <v>434</v>
+      </c>
+      <c r="C114" t="s">
         <v>435</v>
       </c>
-      <c r="B114" t="s">
+      <c r="D114" t="s">
         <v>436</v>
-      </c>
-      <c r="C114" t="s">
-        <v>437</v>
-      </c>
-      <c r="D114" t="s">
-        <v>438</v>
       </c>
       <c r="E114" t="s">
         <v>10</v>
@@ -4639,36 +5526,36 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
+        <v>437</v>
+      </c>
+      <c r="B115" t="s">
+        <v>438</v>
+      </c>
+      <c r="C115" t="s">
         <v>439</v>
       </c>
-      <c r="B115" t="s">
+      <c r="D115" t="s">
         <v>440</v>
-      </c>
-      <c r="C115" t="s">
-        <v>441</v>
-      </c>
-      <c r="D115" t="s">
-        <v>442</v>
       </c>
       <c r="E115" t="s">
         <v>7</v>
       </c>
       <c r="F115" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>442</v>
+      </c>
+      <c r="B116" t="s">
+        <v>443</v>
+      </c>
+      <c r="C116" t="s">
         <v>444</v>
       </c>
-      <c r="B116" t="s">
+      <c r="D116" t="s">
         <v>445</v>
-      </c>
-      <c r="C116" t="s">
-        <v>446</v>
-      </c>
-      <c r="D116" t="s">
-        <v>447</v>
       </c>
       <c r="E116" t="s">
         <v>10</v>
@@ -4676,16 +5563,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
+        <v>446</v>
+      </c>
+      <c r="B117" t="s">
+        <v>447</v>
+      </c>
+      <c r="C117" t="s">
         <v>448</v>
       </c>
-      <c r="B117" t="s">
+      <c r="D117" t="s">
         <v>449</v>
-      </c>
-      <c r="C117" t="s">
-        <v>450</v>
-      </c>
-      <c r="D117" t="s">
-        <v>451</v>
       </c>
       <c r="E117" t="s">
         <v>17</v>
@@ -4693,16 +5580,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
+        <v>450</v>
+      </c>
+      <c r="B118" t="s">
+        <v>451</v>
+      </c>
+      <c r="C118" t="s">
         <v>452</v>
       </c>
-      <c r="B118" t="s">
+      <c r="D118" t="s">
         <v>453</v>
-      </c>
-      <c r="C118" t="s">
-        <v>454</v>
-      </c>
-      <c r="D118" t="s">
-        <v>455</v>
       </c>
       <c r="E118" t="s">
         <v>7</v>
@@ -4710,36 +5597,36 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
+        <v>454</v>
+      </c>
+      <c r="B119" t="s">
+        <v>455</v>
+      </c>
+      <c r="C119" t="s">
         <v>456</v>
       </c>
-      <c r="B119" t="s">
+      <c r="D119" t="s">
         <v>457</v>
-      </c>
-      <c r="C119" t="s">
-        <v>458</v>
-      </c>
-      <c r="D119" t="s">
-        <v>459</v>
       </c>
       <c r="E119" t="s">
         <v>10</v>
       </c>
       <c r="F119" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
+        <v>459</v>
+      </c>
+      <c r="B120" t="s">
+        <v>460</v>
+      </c>
+      <c r="C120" t="s">
         <v>461</v>
       </c>
-      <c r="B120" t="s">
+      <c r="D120" t="s">
         <v>462</v>
-      </c>
-      <c r="C120" t="s">
-        <v>463</v>
-      </c>
-      <c r="D120" t="s">
-        <v>464</v>
       </c>
       <c r="E120" t="s">
         <v>7</v>
@@ -4747,16 +5634,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
+        <v>463</v>
+      </c>
+      <c r="B121" t="s">
+        <v>464</v>
+      </c>
+      <c r="C121" t="s">
         <v>465</v>
       </c>
-      <c r="B121" t="s">
+      <c r="D121" t="s">
         <v>466</v>
-      </c>
-      <c r="C121" t="s">
-        <v>467</v>
-      </c>
-      <c r="D121" t="s">
-        <v>468</v>
       </c>
       <c r="E121" t="s">
         <v>17</v>
@@ -4764,16 +5651,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>469</v>
+        <v>668</v>
       </c>
       <c r="B122" t="s">
         <v>71</v>
       </c>
       <c r="C122" t="s">
-        <v>592</v>
+        <v>560</v>
       </c>
       <c r="D122" t="s">
-        <v>646</v>
+        <v>614</v>
       </c>
       <c r="E122" t="s">
         <v>10</v>
@@ -4781,10 +5668,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>470</v>
+        <v>667</v>
       </c>
       <c r="B123" t="s">
-        <v>538</v>
+        <v>506</v>
       </c>
       <c r="C123" t="s">
         <v>71</v>
@@ -4798,16 +5685,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>471</v>
+        <v>666</v>
       </c>
       <c r="B124" t="s">
-        <v>539</v>
+        <v>507</v>
       </c>
       <c r="C124" t="s">
-        <v>593</v>
+        <v>561</v>
       </c>
       <c r="D124" t="s">
-        <v>647</v>
+        <v>615</v>
       </c>
       <c r="E124" t="s">
         <v>7</v>
@@ -4815,7 +5702,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>472</v>
+        <v>59</v>
       </c>
       <c r="B125" t="s">
         <v>118</v>
@@ -4832,56 +5719,56 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>473</v>
+        <v>664</v>
       </c>
       <c r="B126" t="s">
-        <v>540</v>
+        <v>508</v>
       </c>
       <c r="C126" t="s">
-        <v>594</v>
+        <v>562</v>
       </c>
       <c r="D126" t="s">
-        <v>648</v>
+        <v>616</v>
       </c>
       <c r="E126" t="s">
         <v>7</v>
       </c>
       <c r="F126" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>475</v>
+        <v>663</v>
       </c>
       <c r="B127" t="s">
         <v>82</v>
       </c>
       <c r="C127" t="s">
-        <v>595</v>
+        <v>563</v>
       </c>
       <c r="D127" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E127" t="s">
         <v>17</v>
       </c>
       <c r="F127" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>477</v>
+        <v>662</v>
       </c>
       <c r="B128" t="s">
-        <v>541</v>
+        <v>509</v>
       </c>
       <c r="C128" t="s">
-        <v>596</v>
+        <v>564</v>
       </c>
       <c r="D128" t="s">
-        <v>649</v>
+        <v>617</v>
       </c>
       <c r="E128" t="s">
         <v>10</v>
@@ -4889,13 +5776,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>478</v>
+        <v>661</v>
       </c>
       <c r="B129" t="s">
-        <v>542</v>
+        <v>510</v>
       </c>
       <c r="C129" t="s">
-        <v>597</v>
+        <v>565</v>
       </c>
       <c r="D129" t="s">
         <v>71</v>
@@ -4904,18 +5791,18 @@
         <v>17</v>
       </c>
       <c r="F129" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>480</v>
+        <v>660</v>
       </c>
       <c r="B130" t="s">
-        <v>543</v>
+        <v>511</v>
       </c>
       <c r="C130" t="s">
-        <v>598</v>
+        <v>566</v>
       </c>
       <c r="D130" t="s">
         <v>82</v>
@@ -4924,41 +5811,41 @@
         <v>17</v>
       </c>
       <c r="F130" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>482</v>
+        <v>659</v>
       </c>
       <c r="B131" t="s">
-        <v>544</v>
+        <v>512</v>
       </c>
       <c r="C131" t="s">
-        <v>599</v>
+        <v>567</v>
       </c>
       <c r="D131" t="s">
-        <v>650</v>
+        <v>618</v>
       </c>
       <c r="E131" t="s">
         <v>17</v>
       </c>
       <c r="F131" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>484</v>
+        <v>658</v>
       </c>
       <c r="B132" t="s">
-        <v>545</v>
+        <v>513</v>
       </c>
       <c r="C132" t="s">
-        <v>600</v>
+        <v>568</v>
       </c>
       <c r="D132" t="s">
-        <v>651</v>
+        <v>619</v>
       </c>
       <c r="E132" t="s">
         <v>7</v>
@@ -4966,7 +5853,7 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>485</v>
+        <v>657</v>
       </c>
       <c r="B133" t="s">
         <v>82</v>
@@ -4975,7 +5862,7 @@
         <v>71</v>
       </c>
       <c r="D133" t="s">
-        <v>670</v>
+        <v>638</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
@@ -4983,16 +5870,16 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>486</v>
+        <v>656</v>
       </c>
       <c r="B134" t="s">
-        <v>546</v>
+        <v>514</v>
       </c>
       <c r="C134" t="s">
-        <v>601</v>
+        <v>569</v>
       </c>
       <c r="D134" t="s">
-        <v>652</v>
+        <v>620</v>
       </c>
       <c r="E134" t="s">
         <v>17</v>
@@ -5000,16 +5887,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>487</v>
+        <v>655</v>
       </c>
       <c r="B135" t="s">
-        <v>547</v>
+        <v>515</v>
       </c>
       <c r="C135" t="s">
-        <v>602</v>
+        <v>570</v>
       </c>
       <c r="D135" t="s">
-        <v>653</v>
+        <v>621</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
@@ -5017,16 +5904,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>488</v>
+        <v>654</v>
       </c>
       <c r="B136" t="s">
-        <v>548</v>
+        <v>516</v>
       </c>
       <c r="C136" t="s">
-        <v>603</v>
+        <v>571</v>
       </c>
       <c r="D136" t="s">
-        <v>654</v>
+        <v>622</v>
       </c>
       <c r="E136" t="s">
         <v>7</v>
@@ -5034,36 +5921,36 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>489</v>
+        <v>653</v>
       </c>
       <c r="B137" t="s">
-        <v>549</v>
+        <v>517</v>
       </c>
       <c r="C137" t="s">
-        <v>604</v>
+        <v>572</v>
       </c>
       <c r="D137" t="s">
-        <v>655</v>
+        <v>623</v>
       </c>
       <c r="E137" t="s">
         <v>10</v>
       </c>
       <c r="F137" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>491</v>
+        <v>652</v>
       </c>
       <c r="B138" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="C138" t="s">
-        <v>605</v>
+        <v>573</v>
       </c>
       <c r="D138" t="s">
-        <v>656</v>
+        <v>624</v>
       </c>
       <c r="E138" t="s">
         <v>7</v>
@@ -5071,16 +5958,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>492</v>
+        <v>651</v>
       </c>
       <c r="B139" t="s">
-        <v>551</v>
+        <v>519</v>
       </c>
       <c r="C139" t="s">
-        <v>606</v>
+        <v>574</v>
       </c>
       <c r="D139" t="s">
-        <v>657</v>
+        <v>625</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
@@ -5088,16 +5975,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>493</v>
+        <v>650</v>
       </c>
       <c r="B140" t="s">
-        <v>552</v>
+        <v>520</v>
       </c>
       <c r="C140" t="s">
-        <v>607</v>
+        <v>575</v>
       </c>
       <c r="D140" t="s">
-        <v>658</v>
+        <v>626</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
@@ -5105,16 +5992,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>494</v>
+        <v>649</v>
       </c>
       <c r="B141" t="s">
-        <v>553</v>
+        <v>521</v>
       </c>
       <c r="C141" t="s">
-        <v>608</v>
+        <v>576</v>
       </c>
       <c r="D141" t="s">
-        <v>659</v>
+        <v>627</v>
       </c>
       <c r="E141" t="s">
         <v>7</v>
@@ -5122,16 +6009,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>495</v>
+        <v>648</v>
       </c>
       <c r="B142" t="s">
-        <v>554</v>
+        <v>522</v>
       </c>
       <c r="C142" t="s">
-        <v>609</v>
+        <v>577</v>
       </c>
       <c r="D142" t="s">
-        <v>660</v>
+        <v>628</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -5139,56 +6026,56 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>496</v>
+        <v>647</v>
       </c>
       <c r="B143" t="s">
-        <v>555</v>
+        <v>523</v>
       </c>
       <c r="C143" t="s">
-        <v>610</v>
+        <v>578</v>
       </c>
       <c r="D143" t="s">
-        <v>661</v>
+        <v>629</v>
       </c>
       <c r="E143" t="s">
         <v>17</v>
       </c>
       <c r="F143" t="s">
-        <v>497</v>
+        <v>473</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>498</v>
+        <v>33</v>
       </c>
       <c r="B144" t="s">
-        <v>556</v>
+        <v>524</v>
       </c>
       <c r="C144" t="s">
-        <v>611</v>
+        <v>579</v>
       </c>
       <c r="D144" t="s">
-        <v>662</v>
+        <v>630</v>
       </c>
       <c r="E144" t="s">
         <v>7</v>
       </c>
       <c r="F144" t="s">
-        <v>499</v>
+        <v>474</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>500</v>
+        <v>646</v>
       </c>
       <c r="B145" t="s">
-        <v>557</v>
+        <v>525</v>
       </c>
       <c r="C145" t="s">
-        <v>612</v>
+        <v>580</v>
       </c>
       <c r="D145" t="s">
-        <v>663</v>
+        <v>631</v>
       </c>
       <c r="E145" t="s">
         <v>17</v>
@@ -5196,16 +6083,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>501</v>
+        <v>644</v>
       </c>
       <c r="B146" t="s">
-        <v>558</v>
+        <v>526</v>
       </c>
       <c r="C146" t="s">
-        <v>613</v>
+        <v>581</v>
       </c>
       <c r="D146" t="s">
-        <v>664</v>
+        <v>632</v>
       </c>
       <c r="E146" t="s">
         <v>17</v>
@@ -5213,16 +6100,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>502</v>
+        <v>643</v>
       </c>
       <c r="B147" t="s">
-        <v>559</v>
+        <v>527</v>
       </c>
       <c r="C147" t="s">
-        <v>614</v>
+        <v>582</v>
       </c>
       <c r="D147" t="s">
-        <v>665</v>
+        <v>633</v>
       </c>
       <c r="E147" t="s">
         <v>17</v>
@@ -5230,16 +6117,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>503</v>
+        <v>642</v>
       </c>
       <c r="B148" t="s">
-        <v>560</v>
+        <v>528</v>
       </c>
       <c r="C148" t="s">
-        <v>615</v>
+        <v>583</v>
       </c>
       <c r="D148" t="s">
-        <v>666</v>
+        <v>634</v>
       </c>
       <c r="E148" t="s">
         <v>7</v>
@@ -5247,36 +6134,36 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>504</v>
+        <v>641</v>
       </c>
       <c r="B149" t="s">
-        <v>561</v>
+        <v>529</v>
       </c>
       <c r="C149" t="s">
-        <v>616</v>
+        <v>584</v>
       </c>
       <c r="D149" t="s">
-        <v>667</v>
+        <v>635</v>
       </c>
       <c r="E149" t="s">
         <v>17</v>
       </c>
       <c r="F149" t="s">
-        <v>505</v>
+        <v>475</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>506</v>
+        <v>640</v>
       </c>
       <c r="B150" t="s">
-        <v>562</v>
+        <v>530</v>
       </c>
       <c r="C150" t="s">
-        <v>617</v>
+        <v>585</v>
       </c>
       <c r="D150" t="s">
-        <v>668</v>
+        <v>636</v>
       </c>
       <c r="E150" t="s">
         <v>7</v>
@@ -5284,40 +6171,1300 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>507</v>
+        <v>639</v>
       </c>
       <c r="B151" t="s">
-        <v>563</v>
+        <v>531</v>
       </c>
       <c r="C151" t="s">
-        <v>618</v>
+        <v>586</v>
       </c>
       <c r="D151" t="s">
+        <v>637</v>
+      </c>
+      <c r="E151" t="s">
+        <v>17</v>
+      </c>
+      <c r="F151" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
         <v>669</v>
       </c>
-      <c r="E151" t="s">
-        <v>17</v>
-      </c>
-      <c r="F151" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A225"/>
-      <c r="B225"/>
-      <c r="C225"/>
-      <c r="D225"/>
-      <c r="E225"/>
-    </row>
-    <row r="231" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A231"/>
-      <c r="B231"/>
-      <c r="C231"/>
-      <c r="D231"/>
-      <c r="E231"/>
+      <c r="B152" t="s">
+        <v>670</v>
+      </c>
+      <c r="C152" t="s">
+        <v>671</v>
+      </c>
+      <c r="D152" t="s">
+        <v>672</v>
+      </c>
+      <c r="E152" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>673</v>
+      </c>
+      <c r="B153" t="s">
+        <v>674</v>
+      </c>
+      <c r="C153" t="s">
+        <v>675</v>
+      </c>
+      <c r="D153" t="s">
+        <v>676</v>
+      </c>
+      <c r="E153" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>677</v>
+      </c>
+      <c r="B154" t="s">
+        <v>678</v>
+      </c>
+      <c r="C154" t="s">
+        <v>679</v>
+      </c>
+      <c r="D154" t="s">
+        <v>680</v>
+      </c>
+      <c r="E154" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>685</v>
+      </c>
+      <c r="B156" t="s">
+        <v>686</v>
+      </c>
+      <c r="C156" t="s">
+        <v>687</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="E156" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>689</v>
+      </c>
+      <c r="B157" t="s">
+        <v>690</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="D157" t="s">
+        <v>692</v>
+      </c>
+      <c r="E157" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="E158" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="E160" t="s">
+        <v>17</v>
+      </c>
+      <c r="F160" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>710</v>
+      </c>
+      <c r="B162" t="s">
+        <v>711</v>
+      </c>
+      <c r="C162" t="s">
+        <v>712</v>
+      </c>
+      <c r="D162" t="s">
+        <v>713</v>
+      </c>
+      <c r="E162" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>714</v>
+      </c>
+      <c r="B163" t="s">
+        <v>715</v>
+      </c>
+      <c r="C163" t="s">
+        <v>716</v>
+      </c>
+      <c r="D163" t="s">
+        <v>717</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F163" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>719</v>
+      </c>
+      <c r="B164" t="s">
+        <v>720</v>
+      </c>
+      <c r="C164" t="s">
+        <v>721</v>
+      </c>
+      <c r="D164" t="s">
+        <v>722</v>
+      </c>
+      <c r="E164" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>723</v>
+      </c>
+      <c r="B165" t="s">
+        <v>724</v>
+      </c>
+      <c r="C165" t="s">
+        <v>725</v>
+      </c>
+      <c r="D165" t="s">
+        <v>726</v>
+      </c>
+      <c r="E165" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>727</v>
+      </c>
+      <c r="B166" t="s">
+        <v>728</v>
+      </c>
+      <c r="C166" t="s">
+        <v>729</v>
+      </c>
+      <c r="D166" t="s">
+        <v>730</v>
+      </c>
+      <c r="E166" t="s">
+        <v>7</v>
+      </c>
+      <c r="F166" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>732</v>
+      </c>
+      <c r="B167" t="s">
+        <v>733</v>
+      </c>
+      <c r="C167" t="s">
+        <v>734</v>
+      </c>
+      <c r="D167" t="s">
+        <v>735</v>
+      </c>
+      <c r="E167" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>736</v>
+      </c>
+      <c r="B168" t="s">
+        <v>737</v>
+      </c>
+      <c r="C168" t="s">
+        <v>738</v>
+      </c>
+      <c r="D168" t="s">
+        <v>739</v>
+      </c>
+      <c r="E168" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>740</v>
+      </c>
+      <c r="B169" t="s">
+        <v>741</v>
+      </c>
+      <c r="C169" t="s">
+        <v>742</v>
+      </c>
+      <c r="D169" t="s">
+        <v>743</v>
+      </c>
+      <c r="E169" t="s">
+        <v>7</v>
+      </c>
+      <c r="F169" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>745</v>
+      </c>
+      <c r="B170" t="s">
+        <v>746</v>
+      </c>
+      <c r="C170" t="s">
+        <v>278</v>
+      </c>
+      <c r="D170" t="s">
+        <v>747</v>
+      </c>
+      <c r="E170" t="s">
+        <v>7</v>
+      </c>
+      <c r="F170" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>749</v>
+      </c>
+      <c r="B171" t="s">
+        <v>750</v>
+      </c>
+      <c r="C171" t="s">
+        <v>751</v>
+      </c>
+      <c r="D171" t="s">
+        <v>752</v>
+      </c>
+      <c r="E171" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>753</v>
+      </c>
+      <c r="B172" t="s">
+        <v>754</v>
+      </c>
+      <c r="C172" t="s">
+        <v>755</v>
+      </c>
+      <c r="D172" t="s">
+        <v>756</v>
+      </c>
+      <c r="E172" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>757</v>
+      </c>
+      <c r="B173" t="s">
+        <v>758</v>
+      </c>
+      <c r="C173" t="s">
+        <v>759</v>
+      </c>
+      <c r="D173" t="s">
+        <v>760</v>
+      </c>
+      <c r="E173" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>761</v>
+      </c>
+      <c r="B174" t="s">
+        <v>762</v>
+      </c>
+      <c r="C174" t="s">
+        <v>763</v>
+      </c>
+      <c r="D174" t="s">
+        <v>764</v>
+      </c>
+      <c r="E174" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>765</v>
+      </c>
+      <c r="B175" t="s">
+        <v>766</v>
+      </c>
+      <c r="C175" t="s">
+        <v>767</v>
+      </c>
+      <c r="D175" t="s">
+        <v>768</v>
+      </c>
+      <c r="E175" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>769</v>
+      </c>
+      <c r="B176" t="s">
+        <v>770</v>
+      </c>
+      <c r="C176" t="s">
+        <v>771</v>
+      </c>
+      <c r="D176" t="s">
+        <v>772</v>
+      </c>
+      <c r="E176" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>773</v>
+      </c>
+      <c r="B177" t="s">
+        <v>774</v>
+      </c>
+      <c r="C177" t="s">
+        <v>775</v>
+      </c>
+      <c r="D177" t="s">
+        <v>776</v>
+      </c>
+      <c r="E177" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>777</v>
+      </c>
+      <c r="B178" t="s">
+        <v>778</v>
+      </c>
+      <c r="C178" t="s">
+        <v>779</v>
+      </c>
+      <c r="D178" t="s">
+        <v>780</v>
+      </c>
+      <c r="E178" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>781</v>
+      </c>
+      <c r="B179" t="s">
+        <v>782</v>
+      </c>
+      <c r="C179" t="s">
+        <v>783</v>
+      </c>
+      <c r="D179" t="s">
+        <v>784</v>
+      </c>
+      <c r="E179" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>785</v>
+      </c>
+      <c r="B180" t="s">
+        <v>786</v>
+      </c>
+      <c r="C180" t="s">
+        <v>787</v>
+      </c>
+      <c r="D180" t="s">
+        <v>788</v>
+      </c>
+      <c r="E180" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>789</v>
+      </c>
+      <c r="B181" t="s">
+        <v>790</v>
+      </c>
+      <c r="C181" t="s">
+        <v>791</v>
+      </c>
+      <c r="D181" t="s">
+        <v>792</v>
+      </c>
+      <c r="E181" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>793</v>
+      </c>
+      <c r="B182" t="s">
+        <v>794</v>
+      </c>
+      <c r="C182" t="s">
+        <v>795</v>
+      </c>
+      <c r="D182" t="s">
+        <v>796</v>
+      </c>
+      <c r="E182" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>797</v>
+      </c>
+      <c r="B183" t="s">
+        <v>798</v>
+      </c>
+      <c r="C183" t="s">
+        <v>799</v>
+      </c>
+      <c r="D183" t="s">
+        <v>800</v>
+      </c>
+      <c r="E183" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>801</v>
+      </c>
+      <c r="B184" t="s">
+        <v>802</v>
+      </c>
+      <c r="C184" t="s">
+        <v>803</v>
+      </c>
+      <c r="D184" t="s">
+        <v>804</v>
+      </c>
+      <c r="E184" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>806</v>
+      </c>
+      <c r="B185" t="s">
+        <v>805</v>
+      </c>
+      <c r="C185" t="s">
+        <v>807</v>
+      </c>
+      <c r="D185" t="s">
+        <v>808</v>
+      </c>
+      <c r="E185" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>809</v>
+      </c>
+      <c r="B186" t="s">
+        <v>810</v>
+      </c>
+      <c r="C186" t="s">
+        <v>811</v>
+      </c>
+      <c r="D186" t="s">
+        <v>82</v>
+      </c>
+      <c r="E186" t="s">
+        <v>10</v>
+      </c>
+      <c r="F186" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>813</v>
+      </c>
+      <c r="B187" t="s">
+        <v>814</v>
+      </c>
+      <c r="C187" t="s">
+        <v>815</v>
+      </c>
+      <c r="D187" t="s">
+        <v>816</v>
+      </c>
+      <c r="E187" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>817</v>
+      </c>
+      <c r="B188" t="s">
+        <v>818</v>
+      </c>
+      <c r="C188" t="s">
+        <v>819</v>
+      </c>
+      <c r="D188" t="s">
+        <v>820</v>
+      </c>
+      <c r="E188" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>821</v>
+      </c>
+      <c r="B189" t="s">
+        <v>822</v>
+      </c>
+      <c r="C189" t="s">
+        <v>823</v>
+      </c>
+      <c r="D189" t="s">
+        <v>824</v>
+      </c>
+      <c r="E189" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>825</v>
+      </c>
+      <c r="B190" t="s">
+        <v>826</v>
+      </c>
+      <c r="C190" t="s">
+        <v>827</v>
+      </c>
+      <c r="D190" t="s">
+        <v>828</v>
+      </c>
+      <c r="E190" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>829</v>
+      </c>
+      <c r="B191" t="s">
+        <v>830</v>
+      </c>
+      <c r="C191" t="s">
+        <v>831</v>
+      </c>
+      <c r="D191" t="s">
+        <v>832</v>
+      </c>
+      <c r="E191" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>833</v>
+      </c>
+      <c r="B192" t="s">
+        <v>834</v>
+      </c>
+      <c r="C192" t="s">
+        <v>835</v>
+      </c>
+      <c r="D192" t="s">
+        <v>836</v>
+      </c>
+      <c r="E192" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>837</v>
+      </c>
+      <c r="B193" t="s">
+        <v>838</v>
+      </c>
+      <c r="C193" t="s">
+        <v>839</v>
+      </c>
+      <c r="D193" t="s">
+        <v>840</v>
+      </c>
+      <c r="E193" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>841</v>
+      </c>
+      <c r="B194" t="s">
+        <v>842</v>
+      </c>
+      <c r="C194" t="s">
+        <v>843</v>
+      </c>
+      <c r="D194" t="s">
+        <v>844</v>
+      </c>
+      <c r="E194" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>845</v>
+      </c>
+      <c r="B195" t="s">
+        <v>846</v>
+      </c>
+      <c r="C195" t="s">
+        <v>847</v>
+      </c>
+      <c r="D195" t="s">
+        <v>848</v>
+      </c>
+      <c r="E195" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>849</v>
+      </c>
+      <c r="B196" t="s">
+        <v>850</v>
+      </c>
+      <c r="C196" t="s">
+        <v>851</v>
+      </c>
+      <c r="D196" t="s">
+        <v>852</v>
+      </c>
+      <c r="E196" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>853</v>
+      </c>
+      <c r="B197" t="s">
+        <v>854</v>
+      </c>
+      <c r="C197" t="s">
+        <v>855</v>
+      </c>
+      <c r="D197" t="s">
+        <v>856</v>
+      </c>
+      <c r="E197" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>857</v>
+      </c>
+      <c r="B198" t="s">
+        <v>858</v>
+      </c>
+      <c r="C198" t="s">
+        <v>859</v>
+      </c>
+      <c r="D198" t="s">
+        <v>860</v>
+      </c>
+      <c r="E198" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>861</v>
+      </c>
+      <c r="B199" t="s">
+        <v>862</v>
+      </c>
+      <c r="C199" t="s">
+        <v>863</v>
+      </c>
+      <c r="D199" t="s">
+        <v>864</v>
+      </c>
+      <c r="E199" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>865</v>
+      </c>
+      <c r="B200" t="s">
+        <v>866</v>
+      </c>
+      <c r="C200" t="s">
+        <v>82</v>
+      </c>
+      <c r="D200" t="s">
+        <v>382</v>
+      </c>
+      <c r="E200" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>867</v>
+      </c>
+      <c r="B201" t="s">
+        <v>868</v>
+      </c>
+      <c r="C201" t="s">
+        <v>869</v>
+      </c>
+      <c r="D201" t="s">
+        <v>870</v>
+      </c>
+      <c r="E201" t="s">
+        <v>7</v>
+      </c>
+      <c r="F201" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>872</v>
+      </c>
+      <c r="B202" t="s">
+        <v>873</v>
+      </c>
+      <c r="C202" t="s">
+        <v>874</v>
+      </c>
+      <c r="D202" t="s">
+        <v>875</v>
+      </c>
+      <c r="E202" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>876</v>
+      </c>
+      <c r="B203" t="s">
+        <v>485</v>
+      </c>
+      <c r="C203" t="s">
+        <v>877</v>
+      </c>
+      <c r="D203" t="s">
+        <v>878</v>
+      </c>
+      <c r="E203" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>879</v>
+      </c>
+      <c r="B204" t="s">
+        <v>880</v>
+      </c>
+      <c r="C204" t="s">
+        <v>881</v>
+      </c>
+      <c r="D204" t="s">
+        <v>882</v>
+      </c>
+      <c r="E204" t="s">
+        <v>7</v>
+      </c>
+      <c r="F204" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>884</v>
+      </c>
+      <c r="B205" t="s">
+        <v>885</v>
+      </c>
+      <c r="C205" t="s">
+        <v>886</v>
+      </c>
+      <c r="D205" t="s">
+        <v>887</v>
+      </c>
+      <c r="E205" t="s">
+        <v>17</v>
+      </c>
+      <c r="F205" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>889</v>
+      </c>
+      <c r="B206" t="s">
+        <v>890</v>
+      </c>
+      <c r="C206" t="s">
+        <v>891</v>
+      </c>
+      <c r="D206" t="s">
+        <v>892</v>
+      </c>
+      <c r="E206" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>893</v>
+      </c>
+      <c r="B207" t="s">
+        <v>894</v>
+      </c>
+      <c r="C207" t="s">
+        <v>895</v>
+      </c>
+      <c r="D207" t="s">
+        <v>896</v>
+      </c>
+      <c r="E207" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>897</v>
+      </c>
+      <c r="B208" t="s">
+        <v>898</v>
+      </c>
+      <c r="C208" t="s">
+        <v>899</v>
+      </c>
+      <c r="D208" t="s">
+        <v>900</v>
+      </c>
+      <c r="E208" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>901</v>
+      </c>
+      <c r="B209" t="s">
+        <v>902</v>
+      </c>
+      <c r="C209" t="s">
+        <v>903</v>
+      </c>
+      <c r="D209" t="s">
+        <v>904</v>
+      </c>
+      <c r="E209" t="s">
+        <v>10</v>
+      </c>
+      <c r="F209" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>906</v>
+      </c>
+      <c r="B210" t="s">
+        <v>907</v>
+      </c>
+      <c r="C210" t="s">
+        <v>908</v>
+      </c>
+      <c r="D210" t="s">
+        <v>909</v>
+      </c>
+      <c r="E210" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>910</v>
+      </c>
+      <c r="B211" t="s">
+        <v>911</v>
+      </c>
+      <c r="C211" t="s">
+        <v>912</v>
+      </c>
+      <c r="D211" t="s">
+        <v>913</v>
+      </c>
+      <c r="E211" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>914</v>
+      </c>
+      <c r="B212" t="s">
+        <v>915</v>
+      </c>
+      <c r="C212" t="s">
+        <v>916</v>
+      </c>
+      <c r="D212" t="s">
+        <v>917</v>
+      </c>
+      <c r="E212" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>918</v>
+      </c>
+      <c r="B213" t="s">
+        <v>919</v>
+      </c>
+      <c r="C213" t="s">
+        <v>920</v>
+      </c>
+      <c r="D213" t="s">
+        <v>921</v>
+      </c>
+      <c r="E213" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>922</v>
+      </c>
+      <c r="B214" t="s">
+        <v>923</v>
+      </c>
+      <c r="C214" t="s">
+        <v>924</v>
+      </c>
+      <c r="D214" t="s">
+        <v>925</v>
+      </c>
+      <c r="E214" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>926</v>
+      </c>
+      <c r="B215" t="s">
+        <v>927</v>
+      </c>
+      <c r="C215" t="s">
+        <v>928</v>
+      </c>
+      <c r="D215" t="s">
+        <v>929</v>
+      </c>
+      <c r="E215" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>930</v>
+      </c>
+      <c r="B216" t="s">
+        <v>931</v>
+      </c>
+      <c r="C216" t="s">
+        <v>932</v>
+      </c>
+      <c r="D216" t="s">
+        <v>933</v>
+      </c>
+      <c r="E216" t="s">
+        <v>17</v>
+      </c>
+      <c r="F216" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>935</v>
+      </c>
+      <c r="B217" t="s">
+        <v>936</v>
+      </c>
+      <c r="C217" t="s">
+        <v>937</v>
+      </c>
+      <c r="D217" t="s">
+        <v>938</v>
+      </c>
+      <c r="E217" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>939</v>
+      </c>
+      <c r="B218" t="s">
+        <v>940</v>
+      </c>
+      <c r="C218" t="s">
+        <v>941</v>
+      </c>
+      <c r="D218" t="s">
+        <v>942</v>
+      </c>
+      <c r="E218" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>943</v>
+      </c>
+      <c r="B219" t="s">
+        <v>944</v>
+      </c>
+      <c r="C219" t="s">
+        <v>945</v>
+      </c>
+      <c r="D219" t="s">
+        <v>946</v>
+      </c>
+      <c r="E219" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>947</v>
+      </c>
+      <c r="B220" t="s">
+        <v>948</v>
+      </c>
+      <c r="C220" t="s">
+        <v>949</v>
+      </c>
+      <c r="D220" t="s">
+        <v>950</v>
+      </c>
+      <c r="E220" t="s">
+        <v>17</v>
+      </c>
+      <c r="F220" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>952</v>
+      </c>
+      <c r="B221" t="s">
+        <v>953</v>
+      </c>
+      <c r="C221" t="s">
+        <v>954</v>
+      </c>
+      <c r="D221" t="s">
+        <v>139</v>
+      </c>
+      <c r="E221" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>955</v>
+      </c>
+      <c r="B222" t="s">
+        <v>956</v>
+      </c>
+      <c r="C222" t="s">
+        <v>957</v>
+      </c>
+      <c r="D222" t="s">
+        <v>958</v>
+      </c>
+      <c r="E222" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>959</v>
+      </c>
+      <c r="B223" t="s">
+        <v>71</v>
+      </c>
+      <c r="C223" t="s">
+        <v>960</v>
+      </c>
+      <c r="D223" t="s">
+        <v>961</v>
+      </c>
+      <c r="E223" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A265"/>
+      <c r="B265"/>
+      <c r="C265"/>
+      <c r="D265"/>
+      <c r="E265"/>
+    </row>
+    <row r="271" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A271"/>
+      <c r="B271"/>
+      <c r="C271"/>
+      <c r="D271"/>
+      <c r="E271"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E391" xr:uid="{AA7778BF-C4D9-8B46-A8CD-4B3F292AD9D0}"/>
+  <autoFilter ref="A1:E431" xr:uid="{AA7778BF-C4D9-8B46-A8CD-4B3F292AD9D0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datos/Practica Test.xlsx
+++ b/datos/Practica Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorge/Desktop/AUTOESCUELA/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BCDDD3-F0E7-8540-A25A-26BBC2C99E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F808E9B-F1DB-C940-978E-F5083B05CFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="23220" windowHeight="16820" xr2:uid="{AE6512D7-AD52-4543-8CDE-87DCF5042393}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="T20" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20'!$A$1:$E$431</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20'!$A$1:$E$452</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="1056">
   <si>
     <t>Pregunta</t>
   </si>
@@ -2925,6 +2925,288 @@
   </si>
   <si>
     <t>Sí, pero sólo en vías urbanas.</t>
+  </si>
+  <si>
+    <t>Si existen semáforos con indicaciones distintas a la derecha y a la izquierda, ¿a cuál obedecerán los que pretendan seguir de frente?</t>
+  </si>
+  <si>
+    <t>Al situado a su derecha.</t>
+  </si>
+  <si>
+    <t>Al que se encuentre más cerca del vehículo.</t>
+  </si>
+  <si>
+    <t>Al situado inmediatamente a su izquierda.</t>
+  </si>
+  <si>
+    <t>imagenes/OCT2501.png</t>
+  </si>
+  <si>
+    <t>En el centro de la calzada hay doble línea continua; ¿qué indica?</t>
+  </si>
+  <si>
+    <t>Que la calzada es peligrosa.</t>
+  </si>
+  <si>
+    <t>Que hay un carril especial.</t>
+  </si>
+  <si>
+    <t>Que no se puede atravesar, ni pisar la línea.</t>
+  </si>
+  <si>
+    <t>imagenes/OCT2502.png</t>
+  </si>
+  <si>
+    <t>Al cruzar un arcén por el que transitan peatones, ¿qué debe hacer?</t>
+  </si>
+  <si>
+    <t>Avisarles mediante señales acústicas para que se aparten.</t>
+  </si>
+  <si>
+    <t>Cederles el paso, pero solamente si forman un grupo.</t>
+  </si>
+  <si>
+    <t>Cederles el paso si no disponen de zona peatonal.</t>
+  </si>
+  <si>
+    <t>imagenes/OCT2503.png</t>
+  </si>
+  <si>
+    <t>Esta señal, ¿prohíbe cambiar de dirección a la izquierda?</t>
+  </si>
+  <si>
+    <t>Sí, pero no prohíbe girar a la derecha.</t>
+  </si>
+  <si>
+    <t>Sí; prohíbe realizar cualquier giro.</t>
+  </si>
+  <si>
+    <t>imagenes/OCT2504.png</t>
+  </si>
+  <si>
+    <t>Un furgón, ¿puede utilizar un carril reversible?</t>
+  </si>
+  <si>
+    <t>Solo si su M.M.no es superior a 3.500 kilogramos.</t>
+  </si>
+  <si>
+    <t>imagenes/OCT2505.png</t>
+  </si>
+  <si>
+    <t>Como norma general, en la parte transitable del arcén de una vía interurbana, ¿está permitida la parada o el estacionamiento?</t>
+  </si>
+  <si>
+    <t>Está permitida la parada, pero no el estacionamiento.</t>
+  </si>
+  <si>
+    <t>Está prohibida tanto la parada como el estacionamiento.</t>
+  </si>
+  <si>
+    <t>Está permitida tanto la parada como el estacionamiento.</t>
+  </si>
+  <si>
+    <t>imagenes/OCT2506.png</t>
+  </si>
+  <si>
+    <t>Circulando por una autopista observa que se ha pasado una salida, ¿puede volver a ella circulando marcha atrás?</t>
+  </si>
+  <si>
+    <t>Sí, cuando el recorrido no supere los 15 metros.</t>
+  </si>
+  <si>
+    <t>Sí, comprobando que no existe peligro para otros usuarios.</t>
+  </si>
+  <si>
+    <t>imagenes/OCT2507.png</t>
+  </si>
+  <si>
+    <t>¿Puede circular con su turismo si el equipaje no permite una visión adecuada de la vía por el espejo retrovisor interior?</t>
+  </si>
+  <si>
+    <t>No; en ningún caso la carga puede disminuir la visibilidad a través del espejo retrovisor.</t>
+  </si>
+  <si>
+    <t>Sí, si el vehículo lleva dos espejos retrovisores exteriores, uno a cada lado.</t>
+  </si>
+  <si>
+    <t>Solo si el retrovisor derecho es gran angular y el interior es panorámico.</t>
+  </si>
+  <si>
+    <t>imagenes/OCT2508.png</t>
+  </si>
+  <si>
+    <t>¿Qué significado tiene esta señal?</t>
+  </si>
+  <si>
+    <t>Peligro por la proximidad de un paso a nivel provisto de barreras o semibarreras.</t>
+  </si>
+  <si>
+    <t>Peligro por la proximidad de un paso a nivel sin barreras de más de una vía férrea.</t>
+  </si>
+  <si>
+    <t>Peligro por la proximidad de un cruce con una línea de tranvía.</t>
+  </si>
+  <si>
+    <t>imagenes/OCT2509.png</t>
+  </si>
+  <si>
+    <t>En general, un conductor con sueño...</t>
+  </si>
+  <si>
+    <t>acepta un mayor nivel de riesgo en la conducción.</t>
+  </si>
+  <si>
+    <t>acepta un menor nivel de riesgo en la conducción.</t>
+  </si>
+  <si>
+    <t>tarda menos en reaccionar ante un suceso imprevisto.</t>
+  </si>
+  <si>
+    <t>¿Cómo se conocen a los colectivos de personas que tienen una mayor probabilidad de verse implicados en un accidente de tráfico o de fallecer a consecuencia del mismo?</t>
+  </si>
+  <si>
+    <t>Grupos de riesgo o vulnerables en el tráfico.</t>
+  </si>
+  <si>
+    <t>Víctimas de accidentes de tráfico.</t>
+  </si>
+  <si>
+    <t>Grupos en riesgo de exclusión social.</t>
+  </si>
+  <si>
+    <t>¿Puede sobresalir por la parte trasera del vehículo la carga indivisible que transporta un turismo?</t>
+  </si>
+  <si>
+    <t>Sí, un máximo de hasta el 10% de la longitud del vehículo.</t>
+  </si>
+  <si>
+    <t>No, la carga no puede sobresalir por la parte trasera de un turismo.</t>
+  </si>
+  <si>
+    <t>Sí, un máximo de hasta el 15% de la longitud del vehículo.</t>
+  </si>
+  <si>
+    <t>Si queda detenido en un atasco, ¿qué distancia es aconsejable mantener con el vehículo de delante?</t>
+  </si>
+  <si>
+    <t>Un metro como máximo.</t>
+  </si>
+  <si>
+    <t>Un espacio mínimo para ocupar menos espacio.</t>
+  </si>
+  <si>
+    <t>Dos o tres metros para no golpear al vehículo de delante en caso de alcance trasero.</t>
+  </si>
+  <si>
+    <t>¿Qué condiciones deben tener los neumáticos de una motocicleta?</t>
+  </si>
+  <si>
+    <t>Las dos ruedas tienen que ser del mismo tamaño y características.</t>
+  </si>
+  <si>
+    <t>Las ranuras de la banda de rodadura deben tener una profundidad mínima de 1,6 milímetros.</t>
+  </si>
+  <si>
+    <t>No deben presentar ampollas, deformaciones anormales o roturas.</t>
+  </si>
+  <si>
+    <t>Los impedidos que se desplacen en silla de ruedas por el arcén de una vía, ¿están obligados a obedecer las señales dirigidas a los conductores de vehículos?</t>
+  </si>
+  <si>
+    <t>Sí, las de los agentes y semáforos, siempre.</t>
+  </si>
+  <si>
+    <t>Sí, todas.</t>
+  </si>
+  <si>
+    <t>No, porque son peatones.</t>
+  </si>
+  <si>
+    <t>En el caso de perder todos los puntos del permiso de conducir, ¿qué situación conllevará?</t>
+  </si>
+  <si>
+    <t>No conllevará ningún efecto.</t>
+  </si>
+  <si>
+    <t>Únicamente la suspensión de este.</t>
+  </si>
+  <si>
+    <t>Su pérdida de vigencia.</t>
+  </si>
+  <si>
+    <t>Los remolques no ligeros con más de dos años de antigüedad, ¿deben pasar la ITV?</t>
+  </si>
+  <si>
+    <t>Sí, cuando deba pasar la ITV el automóvil al que van enganchados.</t>
+  </si>
+  <si>
+    <t>Sí, cada dos años.</t>
+  </si>
+  <si>
+    <t>Como norma general, ¿dónde está prohibido adelantar?</t>
+  </si>
+  <si>
+    <t>En las vías de un carril para cada sentido.</t>
+  </si>
+  <si>
+    <t>En los pasos para peatones y cerca de ellos.</t>
+  </si>
+  <si>
+    <t>En las vías de menos de 6 metros de anchura.</t>
+  </si>
+  <si>
+    <t>Mediante el empleo de la correspondiente señalización, las velocidades máximas en autovías dentro de poblado podrán ser...</t>
+  </si>
+  <si>
+    <t>ampliadas sin rebasar, en ningún caso, los límites genéricos establecidos para dichas vías fuera de poblado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rebajadas o ampliadas rebasando incluso los límites genéricos establecidos para dichas vías fuera de poblado. </t>
+  </si>
+  <si>
+    <t>únicamente rebajadas en autovías especialmente peligrosas.</t>
+  </si>
+  <si>
+    <t>Un remolque de la categoría 02 que no es una caravana remolcada y está destinado al transporte de mercancías, debe someterse a la inspección técnica periódica hasta que tenga una antigüedad de 10 años...</t>
+  </si>
+  <si>
+    <t>cada cuatro años.</t>
+  </si>
+  <si>
+    <t>cada dos años.</t>
+  </si>
+  <si>
+    <t>cada año.</t>
+  </si>
+  <si>
+    <t>No, si no es una discusión fuerte.</t>
+  </si>
+  <si>
+    <t>Sí, pero lo mejora, pues disminuye.</t>
+  </si>
+  <si>
+    <t>Si la furgoneta dispone de un mando para regular las luces, ¿debe su conductor, si es necesario, regular las luces cuando transporte carga pesada?</t>
+  </si>
+  <si>
+    <t>No, si el peso está distribuido uniformemente.</t>
+  </si>
+  <si>
+    <t>No, normalmente las luces se adaptan a la carga.</t>
+  </si>
+  <si>
+    <t>¿Es conveniente hacer una revisión exhaustiva del estado del vehículo si el humo que despide el tubo de escape es de color negro?</t>
+  </si>
+  <si>
+    <t>Sí, porque en este caso puede deberse a una mala combustión.</t>
+  </si>
+  <si>
+    <t>Sí, porque el motor puede estar quemando aceite.</t>
+  </si>
+  <si>
+    <t>No, porque solo es un problema de refrigeración que suele desaparecer.</t>
+  </si>
+  <si>
+    <t>Discutir con un acompañante, ¿puede alterar el tiempo de reacción del conductor?</t>
   </si>
 </sst>
 </file>
@@ -3318,7 +3600,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7778BF-C4D9-8B46-A8CD-4B3F292AD9D0}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:F271"/>
+  <dimension ref="A1:F292"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.5" bestFit="1" customWidth="1"/>
@@ -7449,22 +7731,440 @@
         <v>7</v>
       </c>
     </row>
-    <row r="265" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A265"/>
-      <c r="B265"/>
-      <c r="C265"/>
-      <c r="D265"/>
-      <c r="E265"/>
-    </row>
-    <row r="271" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A271"/>
-      <c r="B271"/>
-      <c r="C271"/>
-      <c r="D271"/>
-      <c r="E271"/>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>962</v>
+      </c>
+      <c r="B224" t="s">
+        <v>963</v>
+      </c>
+      <c r="C224" t="s">
+        <v>964</v>
+      </c>
+      <c r="D224" t="s">
+        <v>965</v>
+      </c>
+      <c r="E224" t="s">
+        <v>17</v>
+      </c>
+      <c r="F224" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>967</v>
+      </c>
+      <c r="B225" t="s">
+        <v>968</v>
+      </c>
+      <c r="C225" t="s">
+        <v>969</v>
+      </c>
+      <c r="D225" t="s">
+        <v>970</v>
+      </c>
+      <c r="E225" t="s">
+        <v>17</v>
+      </c>
+      <c r="F225" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>972</v>
+      </c>
+      <c r="B226" t="s">
+        <v>973</v>
+      </c>
+      <c r="C226" t="s">
+        <v>974</v>
+      </c>
+      <c r="D226" t="s">
+        <v>975</v>
+      </c>
+      <c r="E226" t="s">
+        <v>17</v>
+      </c>
+      <c r="F226" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>977</v>
+      </c>
+      <c r="B227" t="s">
+        <v>82</v>
+      </c>
+      <c r="C227" t="s">
+        <v>978</v>
+      </c>
+      <c r="D227" t="s">
+        <v>979</v>
+      </c>
+      <c r="E227" t="s">
+        <v>10</v>
+      </c>
+      <c r="F227" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>981</v>
+      </c>
+      <c r="B228" t="s">
+        <v>982</v>
+      </c>
+      <c r="C228" t="s">
+        <v>82</v>
+      </c>
+      <c r="D228" t="s">
+        <v>71</v>
+      </c>
+      <c r="E228" t="s">
+        <v>17</v>
+      </c>
+      <c r="F228" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>984</v>
+      </c>
+      <c r="B229" t="s">
+        <v>985</v>
+      </c>
+      <c r="C229" t="s">
+        <v>986</v>
+      </c>
+      <c r="D229" t="s">
+        <v>987</v>
+      </c>
+      <c r="E229" t="s">
+        <v>17</v>
+      </c>
+      <c r="F229" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>989</v>
+      </c>
+      <c r="B230" t="s">
+        <v>82</v>
+      </c>
+      <c r="C230" t="s">
+        <v>990</v>
+      </c>
+      <c r="D230" t="s">
+        <v>991</v>
+      </c>
+      <c r="E230" t="s">
+        <v>10</v>
+      </c>
+      <c r="F230" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>993</v>
+      </c>
+      <c r="B231" t="s">
+        <v>994</v>
+      </c>
+      <c r="C231" t="s">
+        <v>995</v>
+      </c>
+      <c r="D231" t="s">
+        <v>996</v>
+      </c>
+      <c r="E231" t="s">
+        <v>7</v>
+      </c>
+      <c r="F231" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>998</v>
+      </c>
+      <c r="B232" t="s">
+        <v>999</v>
+      </c>
+      <c r="C232" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D232" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E232" t="s">
+        <v>10</v>
+      </c>
+      <c r="F232" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C233" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E233" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B234" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C234" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D234" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E234" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B235" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C235" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D235" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E235" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B236" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C236" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D236" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E236" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B237" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C237" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D237" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E237" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B238" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C238" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D238" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E238" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C239" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D239" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E239" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B240" t="s">
+        <v>71</v>
+      </c>
+      <c r="C240" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D240" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E240" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B241" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C241" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D241" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E241" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B242" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C242" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D242" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E242" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B243" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C243" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D243" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E243" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C244" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D244" t="s">
+        <v>71</v>
+      </c>
+      <c r="E244" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B245" t="s">
+        <v>71</v>
+      </c>
+      <c r="C245" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D245" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E245" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C246" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D246" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E246" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A286"/>
+      <c r="B286"/>
+      <c r="C286"/>
+      <c r="D286"/>
+      <c r="E286"/>
+    </row>
+    <row r="292" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A292"/>
+      <c r="B292"/>
+      <c r="C292"/>
+      <c r="D292"/>
+      <c r="E292"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E431" xr:uid="{AA7778BF-C4D9-8B46-A8CD-4B3F292AD9D0}"/>
+  <autoFilter ref="A1:E452" xr:uid="{AA7778BF-C4D9-8B46-A8CD-4B3F292AD9D0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datos/Practica Test.xlsx
+++ b/datos/Practica Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorge/Desktop/AUTOESCUELA/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F808E9B-F1DB-C940-978E-F5083B05CFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82C9AC5-3DC6-F042-9908-AD03F2AA172F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="23220" windowHeight="16820" xr2:uid="{AE6512D7-AD52-4543-8CDE-87DCF5042393}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="T20" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20'!$A$1:$E$452</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20'!$A$1:$E$493</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="1056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="1218">
   <si>
     <t>Pregunta</t>
   </si>
@@ -2195,9 +2195,6 @@
     <t>A 60 kilómetros por hora.</t>
   </si>
   <si>
-    <t>imágenes/carriladd.png</t>
-  </si>
-  <si>
     <t>La luz antiniebla trasera deberá utilizarse siempre que...</t>
   </si>
   <si>
@@ -3207,6 +3204,495 @@
   </si>
   <si>
     <t>Discutir con un acompañante, ¿puede alterar el tiempo de reacción del conductor?</t>
+  </si>
+  <si>
+    <t>¿En qué tanto por ciento de los accidentes en vía interurbana con víctimas, la velocidad es inadecuada o excesiva?</t>
+  </si>
+  <si>
+    <t>¿Con qué frecuencia se harán las compresiones de un masaje cardíaco?</t>
+  </si>
+  <si>
+    <t>¿Cuáles son los únicos vehículos que pueden no llevar guardabarros?</t>
+  </si>
+  <si>
+    <t>Cuando un conductor profesional pierde por primera vez todos los puntos del carnet, ¿cuándo podrá obtener de nuevo su permiso?</t>
+  </si>
+  <si>
+    <t>¿Cuál de éstas partes del circuito de carga produce corriente continua?</t>
+  </si>
+  <si>
+    <t>La máxima velocidad segura que podrá mantenerse sobre una sección de carretera en condiciones favorables es la velocidad...</t>
+  </si>
+  <si>
+    <t>¿A qué grupo de vehículos especiales pertenece el tractor de servicio?</t>
+  </si>
+  <si>
+    <t>¿Se pueden utilizar las luces de largo alcance para advertir de un adelantamiento en poblado?</t>
+  </si>
+  <si>
+    <t>¿Qué elemento se puede utilizar para eliminar el hielo que se encuentra en un vehículo tras una noche de nevada?</t>
+  </si>
+  <si>
+    <t>¿A qué velocidad máxima podrán circular los turismos ante el nivel amarillo de circulación con nieve?</t>
+  </si>
+  <si>
+    <t>Se encuentra ante una curva de visibilidad reducida con dos sentidos de circulación claramente delimitados. ¿Podrá adelantar a un vehículo en estas circunstancias?</t>
+  </si>
+  <si>
+    <t>En un control preventivo, ¿quiénes están obligados a someterse a las pruebas que se establezcan para la detección de alcoholemia?</t>
+  </si>
+  <si>
+    <t>¿Qué documentación tienen que llevar todos los remolques?</t>
+  </si>
+  <si>
+    <t>¿Cuál de estos NO es un dispositivo de barrera?</t>
+  </si>
+  <si>
+    <t>Es la luz de estacionamiento obligatoria para todos los vehículos de 4 metros?</t>
+  </si>
+  <si>
+    <t>¿Cómo se puede evitar el deslumbramiento en el espejo retrovisor interior?</t>
+  </si>
+  <si>
+    <t>¿Dónde suelen ir colocados los inyectores dentro de un motor?</t>
+  </si>
+  <si>
+    <t>En una intersección con señal de ceda el paso pintada en el suelo y visibilidad reducida, ¿dónde debe detenerse para ceder el paso?</t>
+  </si>
+  <si>
+    <t>¿Están obligados los conductores de bicicleta a llevar casco en rampas prolongadas ascendentes de vía interurbana? (OJO CAMBIA)</t>
+  </si>
+  <si>
+    <t>Si la rueda de repuesto es igual a las demás, ¿Qué presión de inflado deberemos darle?</t>
+  </si>
+  <si>
+    <t>Los accidentes de tráfico representan una de las principales causas de mortalidad, que concierne principalmente a...</t>
+  </si>
+  <si>
+    <t>¿A cuántas revoluciones por minuto aproximadamente debe girar el motor durante el arranque en un motor de encendido por chispa?</t>
+  </si>
+  <si>
+    <t>Esta señal...</t>
+  </si>
+  <si>
+    <t>¿A qué velocidad se producen la mayor parte de accidentes graves de tráfico?</t>
+  </si>
+  <si>
+    <t>¿En qué lugar debe situarse un vehículo que va a ser adelantado por la derecha en una vía de doble sentido?</t>
+  </si>
+  <si>
+    <t>26. ¿Circular no rebasando las limitaciones de velocidad es igual a conducir a una velocidad segura?</t>
+  </si>
+  <si>
+    <t>27. Los agentes podrán someter a la prueba de detección de estupefacientes, u otras sustancias análogas a...</t>
+  </si>
+  <si>
+    <t>28. ¿De qué tanto por ciento de accidentes es responsable la distracción al volante?</t>
+  </si>
+  <si>
+    <t>29. ¿A qué velocidad como máximo podremos circular en el preciso instante en el que observamos esta señal?</t>
+  </si>
+  <si>
+    <t>30. El sistema ADAS conocido con el nombre de “Información de ángulo muerto”, ¿puede intervenir en la conducción del vehículo?</t>
+  </si>
+  <si>
+    <t>imagenes/carriladd.png</t>
+  </si>
+  <si>
+    <t>imagenes/sautovia.png</t>
+  </si>
+  <si>
+    <t>En un tercio de los accidentes</t>
+  </si>
+  <si>
+    <t>100 compresiones por minuto.</t>
+  </si>
+  <si>
+    <t>Los tractores agrícolas</t>
+  </si>
+  <si>
+    <t>2 años</t>
+  </si>
+  <si>
+    <t>Regulador de voltaje.</t>
+  </si>
+  <si>
+    <t>adecuada de una vía.</t>
+  </si>
+  <si>
+    <t>Vehículos especiales agrícolas autopropulsados</t>
+  </si>
+  <si>
+    <t>Sí, pero en ráfagas cortas</t>
+  </si>
+  <si>
+    <t>Alcohol</t>
+  </si>
+  <si>
+    <t>A 50 km por hora</t>
+  </si>
+  <si>
+    <t>Sí, siempre que la maniobra se haga con seguridad.</t>
+  </si>
+  <si>
+    <t>Los conductores de bicicletas.</t>
+  </si>
+  <si>
+    <t>Solamente el permiso de circulación</t>
+  </si>
+  <si>
+    <t>Luces amarillas intermitentes</t>
+  </si>
+  <si>
+    <t>Modificando 90 grados la posición del retrovisor hacia el lado izquierdo.</t>
+  </si>
+  <si>
+    <t>En la bomba de inyección</t>
+  </si>
+  <si>
+    <t>Primero antes de la línea y después donde vea bien la intersección.</t>
+  </si>
+  <si>
+    <t>No, no estarán obligados.</t>
+  </si>
+  <si>
+    <t>La recomendada por el fabricante para el resto de las ruedas.</t>
+  </si>
+  <si>
+    <t>Los nuevos conductores.</t>
+  </si>
+  <si>
+    <t>500 rpm</t>
+  </si>
+  <si>
+    <t>prohíbe cambiar de dirección y de sentido.</t>
+  </si>
+  <si>
+    <t>Entre 100 y 120 km por hora</t>
+  </si>
+  <si>
+    <t>En el centro de la calzada sin rebasar el eje de la misma</t>
+  </si>
+  <si>
+    <t>Depende de la situación</t>
+  </si>
+  <si>
+    <t>cualquier usuario de la vía o conductor de vehículo.</t>
+  </si>
+  <si>
+    <t>Del 40 % de los accidentes</t>
+  </si>
+  <si>
+    <t>No, este sistema únicamente emite avisos al conductor de manera sonora.</t>
+  </si>
+  <si>
+    <t>En el 85% de los accidentes</t>
+  </si>
+  <si>
+    <t>50 compresiones por minuto.</t>
+  </si>
+  <si>
+    <t>Los vehículos especiales</t>
+  </si>
+  <si>
+    <t>3 meses</t>
+  </si>
+  <si>
+    <t>Alternador.</t>
+  </si>
+  <si>
+    <t>de fluidez de una vía.</t>
+  </si>
+  <si>
+    <t>Vehículos especiales autopropulsados para obras y servicios</t>
+  </si>
+  <si>
+    <t>Sí, con ráfagas prolongadas</t>
+  </si>
+  <si>
+    <t>Agua destilada</t>
+  </si>
+  <si>
+    <t>A 60 km por hora</t>
+  </si>
+  <si>
+    <t>No, en ningún caso.</t>
+  </si>
+  <si>
+    <t>Todos los usuarios de la vía aunque no hayan cometido una infracción.</t>
+  </si>
+  <si>
+    <t>El permiso de circulación y la tarjeta ITV</t>
+  </si>
+  <si>
+    <t>Luz roja intermitente</t>
+  </si>
+  <si>
+    <t>Sí, pero solo puede ser utilizada durante el día</t>
+  </si>
+  <si>
+    <t>Poniendo la mano frente a él.</t>
+  </si>
+  <si>
+    <t>En el colector de admisión</t>
+  </si>
+  <si>
+    <t>Donde vea bien la otra vía, pero sin poner en peligro a otros conductores.</t>
+  </si>
+  <si>
+    <t>Sí, como norma general.</t>
+  </si>
+  <si>
+    <t>La más baja de las fijadas por el fabricante.</t>
+  </si>
+  <si>
+    <t>Conductores mayores de 45 años.</t>
+  </si>
+  <si>
+    <t>1550 rpm</t>
+  </si>
+  <si>
+    <t>indica sentido obligatorio en una vía de uno o más carriles.</t>
+  </si>
+  <si>
+    <t>Entre 50 y 80 km por hora</t>
+  </si>
+  <si>
+    <t>Ceñido al borde derecho de la calzada rebasando el eje de la misma si es necesario</t>
+  </si>
+  <si>
+    <t>cualquier usuario de la vía con síntomas de estar bajo sus efectos.</t>
+  </si>
+  <si>
+    <t>Del 20 % de los accidentes</t>
+  </si>
+  <si>
+    <t>50 km/h.</t>
+  </si>
+  <si>
+    <t>Sí, siempre puede intervenir para evitar una posible colisión o roce.</t>
+  </si>
+  <si>
+    <t>En el 10% de los accidentes</t>
+  </si>
+  <si>
+    <t>30 compresiones por minuto.</t>
+  </si>
+  <si>
+    <t>Los remolques y semiremolques</t>
+  </si>
+  <si>
+    <t>6 meses</t>
+  </si>
+  <si>
+    <t>Batería.</t>
+  </si>
+  <si>
+    <t>de diseño de una vía.</t>
+  </si>
+  <si>
+    <t>Vehículos especiales agrícolas remolcados</t>
+  </si>
+  <si>
+    <t>Liquido anticongelante</t>
+  </si>
+  <si>
+    <t>A 40 km por hora</t>
+  </si>
+  <si>
+    <t>Sí, pero sin invadir el sentido contrario.</t>
+  </si>
+  <si>
+    <t>Únicamente los conductores de vehículos a motor.</t>
+  </si>
+  <si>
+    <t>Únicamente la tarjeta ITV</t>
+  </si>
+  <si>
+    <t>Semibarrera móvil</t>
+  </si>
+  <si>
+    <t>Sí, para todos los vehículos</t>
+  </si>
+  <si>
+    <t>Desplazando bruscamente la cabeza.</t>
+  </si>
+  <si>
+    <t>En el sistema de filtros</t>
+  </si>
+  <si>
+    <t>Siempre antes de la línea discontinua.</t>
+  </si>
+  <si>
+    <t>Solo estarán obligados a llevarlo los menores de siete años.</t>
+  </si>
+  <si>
+    <t>La más alta de las fijadas por el fabricante.</t>
+  </si>
+  <si>
+    <t>Los niños.</t>
+  </si>
+  <si>
+    <t>70 rpm</t>
+  </si>
+  <si>
+    <t>permite cambiar de dirección pero no de sentido.</t>
+  </si>
+  <si>
+    <t>Entre 80 y 100 km por hora</t>
+  </si>
+  <si>
+    <t>Lo más a la izquierda que le sea posible sin rebasar el eje de la calzada</t>
+  </si>
+  <si>
+    <t>Los conductores que sean denunciados por alguna infracción.</t>
+  </si>
+  <si>
+    <t>Del 80 % de los accidentes</t>
+  </si>
+  <si>
+    <t>En ningún caso, ya que el conductor tiene el control absoluto del vehículo en todo momento.</t>
+  </si>
+  <si>
+    <t>Colocándole siempre un collarín cervical</t>
+  </si>
+  <si>
+    <t>Nunca debemos tocar el cuello del accidentado</t>
+  </si>
+  <si>
+    <t>Situando manos у antebrazos a ambos lados de cabeza y cuello</t>
+  </si>
+  <si>
+    <t>¿De qué color es la luz de trabajo de un tractor agrícola?</t>
+  </si>
+  <si>
+    <t>Blanco</t>
+  </si>
+  <si>
+    <t>Rojo</t>
+  </si>
+  <si>
+    <t>Amarillo auto</t>
+  </si>
+  <si>
+    <t>¿Están obligados todos los automóviles destinados al transporte de mercancías con una MMA superior a 3500kg a llevar una rueda de repuesto o kit antipinchazos y las herramientas necesarias para su cambio?</t>
+  </si>
+  <si>
+    <t>Únicamente estarán obligados los autobuses</t>
+  </si>
+  <si>
+    <t>¿Es obligatorio que los automóviles lleven luces de posición lateral?</t>
+  </si>
+  <si>
+    <t>Sólo en aquellos que superen los 6 metros de longitud</t>
+  </si>
+  <si>
+    <t>Sí, en todo tipo de automóviles</t>
+  </si>
+  <si>
+    <t>Sólo en aquellos que superen los 3 metros de longitud</t>
+  </si>
+  <si>
+    <t>¿Está considerada la marcha atrás como una maniobra básica?</t>
+  </si>
+  <si>
+    <t>Sí, sólo en casos de necesidad</t>
+  </si>
+  <si>
+    <t>Sí, y además es una maniobra básica de circulación</t>
+  </si>
+  <si>
+    <t>9. ¿Qué tipo de dispositivo es el panel direccional provisional?</t>
+  </si>
+  <si>
+    <t>Dispositivo de guía</t>
+  </si>
+  <si>
+    <t>Dispositivo de barrera</t>
+  </si>
+  <si>
+    <t>Ninguno de los anteriores</t>
+  </si>
+  <si>
+    <t>¿Cuál de éstas NO es una señal vertical de servicio?</t>
+  </si>
+  <si>
+    <t>Carril reservado para autobuses</t>
+  </si>
+  <si>
+    <t>Base de ambulancia</t>
+  </si>
+  <si>
+    <t>Señal de restauración</t>
+  </si>
+  <si>
+    <t>¿Qué tipo de vehículos especiales están exceptuados de llevar luces indicadoras de dirección de forma obligatoria?</t>
+  </si>
+  <si>
+    <t>Aquellos cuya MMA supere los 4500 kg</t>
+  </si>
+  <si>
+    <t>Aquellos en que se pueda señalizar con el brazo los cambios de dirección</t>
+  </si>
+  <si>
+    <t>Aquellos que realicen trabajos agrícolas</t>
+  </si>
+  <si>
+    <t>¿En qué tipo de recorridos aparecen mas desventajas en el uso del automóvil?</t>
+  </si>
+  <si>
+    <t>Recorridos sinuosos</t>
+  </si>
+  <si>
+    <t>Recorridos cortos</t>
+  </si>
+  <si>
+    <t>Recorridos largos</t>
+  </si>
+  <si>
+    <t>Según los datos de accidentalidad, la mayoría de los peatones víctimas de opello...</t>
+  </si>
+  <si>
+    <t>Cruzaban la calzada por un lugar no destinado al paso de peatones.</t>
+  </si>
+  <si>
+    <t>Cruzaban la calzada sin respetar las indicaciones del semáforo.</t>
+  </si>
+  <si>
+    <t>No habían cometido ninguna infracción.</t>
+  </si>
+  <si>
+    <t>¿Están los vehículos especiales sometidos en su construcción a las normas sobre masas y dimensiones máximas para circular?</t>
+  </si>
+  <si>
+    <t>Únicamente los vehículos especiales de tipo agrícola</t>
+  </si>
+  <si>
+    <t>Sí, todos ellos</t>
+  </si>
+  <si>
+    <t>¿Qué nombre recibe la cadena de acciones que se deben realizar en un accidente de tráfico?</t>
+  </si>
+  <si>
+    <t>Cadena de heridos</t>
+  </si>
+  <si>
+    <t>Cadena de supervivencia</t>
+  </si>
+  <si>
+    <t>Cadena de ayuda</t>
+  </si>
+  <si>
+    <t>Según la norma específica, al aproximarse a un vehículo inmovilizado en la calzada, ¿es obligatorio moderar la velocidad?</t>
+  </si>
+  <si>
+    <t>Sí, en cualquier tipo de vía pública.</t>
+  </si>
+  <si>
+    <t>Sí, en vías fuera de poblado.</t>
+  </si>
+  <si>
+    <t>¿Cómo debemos proteger el cuello para evitar movimientos bruscos que pudieran perjudicar al herido?</t>
   </si>
 </sst>
 </file>
@@ -3600,7 +4086,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7778BF-C4D9-8B46-A8CD-4B3F292AD9D0}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:F292"/>
+  <dimension ref="A1:F333"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.5" bestFit="1" customWidth="1"/>
@@ -6678,21 +7164,21 @@
         <v>10</v>
       </c>
       <c r="F163" t="s">
-        <v>718</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
+        <v>718</v>
+      </c>
+      <c r="B164" t="s">
         <v>719</v>
       </c>
-      <c r="B164" t="s">
+      <c r="C164" t="s">
         <v>720</v>
       </c>
-      <c r="C164" t="s">
+      <c r="D164" t="s">
         <v>721</v>
-      </c>
-      <c r="D164" t="s">
-        <v>722</v>
       </c>
       <c r="E164" t="s">
         <v>17</v>
@@ -6700,16 +7186,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
+        <v>722</v>
+      </c>
+      <c r="B165" t="s">
         <v>723</v>
       </c>
-      <c r="B165" t="s">
+      <c r="C165" t="s">
         <v>724</v>
       </c>
-      <c r="C165" t="s">
+      <c r="D165" t="s">
         <v>725</v>
-      </c>
-      <c r="D165" t="s">
-        <v>726</v>
       </c>
       <c r="E165" t="s">
         <v>17</v>
@@ -6717,36 +7203,36 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
+        <v>726</v>
+      </c>
+      <c r="B166" t="s">
         <v>727</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
         <v>728</v>
       </c>
-      <c r="C166" t="s">
+      <c r="D166" t="s">
         <v>729</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166" t="s">
+        <v>7</v>
+      </c>
+      <c r="F166" t="s">
         <v>730</v>
-      </c>
-      <c r="E166" t="s">
-        <v>7</v>
-      </c>
-      <c r="F166" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
+        <v>731</v>
+      </c>
+      <c r="B167" t="s">
         <v>732</v>
       </c>
-      <c r="B167" t="s">
+      <c r="C167" t="s">
         <v>733</v>
       </c>
-      <c r="C167" t="s">
+      <c r="D167" t="s">
         <v>734</v>
-      </c>
-      <c r="D167" t="s">
-        <v>735</v>
       </c>
       <c r="E167" t="s">
         <v>7</v>
@@ -6754,16 +7240,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
+        <v>735</v>
+      </c>
+      <c r="B168" t="s">
         <v>736</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C168" t="s">
         <v>737</v>
       </c>
-      <c r="C168" t="s">
+      <c r="D168" t="s">
         <v>738</v>
-      </c>
-      <c r="D168" t="s">
-        <v>739</v>
       </c>
       <c r="E168" t="s">
         <v>10</v>
@@ -6771,56 +7257,56 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
+        <v>739</v>
+      </c>
+      <c r="B169" t="s">
         <v>740</v>
       </c>
-      <c r="B169" t="s">
+      <c r="C169" t="s">
         <v>741</v>
       </c>
-      <c r="C169" t="s">
+      <c r="D169" t="s">
         <v>742</v>
       </c>
-      <c r="D169" t="s">
+      <c r="E169" t="s">
+        <v>7</v>
+      </c>
+      <c r="F169" t="s">
         <v>743</v>
-      </c>
-      <c r="E169" t="s">
-        <v>7</v>
-      </c>
-      <c r="F169" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
+        <v>744</v>
+      </c>
+      <c r="B170" t="s">
         <v>745</v>
-      </c>
-      <c r="B170" t="s">
-        <v>746</v>
       </c>
       <c r="C170" t="s">
         <v>278</v>
       </c>
       <c r="D170" t="s">
+        <v>746</v>
+      </c>
+      <c r="E170" t="s">
+        <v>7</v>
+      </c>
+      <c r="F170" t="s">
         <v>747</v>
-      </c>
-      <c r="E170" t="s">
-        <v>7</v>
-      </c>
-      <c r="F170" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
+        <v>748</v>
+      </c>
+      <c r="B171" t="s">
         <v>749</v>
       </c>
-      <c r="B171" t="s">
+      <c r="C171" t="s">
         <v>750</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
         <v>751</v>
-      </c>
-      <c r="D171" t="s">
-        <v>752</v>
       </c>
       <c r="E171" t="s">
         <v>17</v>
@@ -6828,16 +7314,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
+        <v>752</v>
+      </c>
+      <c r="B172" t="s">
         <v>753</v>
       </c>
-      <c r="B172" t="s">
+      <c r="C172" t="s">
         <v>754</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
         <v>755</v>
-      </c>
-      <c r="D172" t="s">
-        <v>756</v>
       </c>
       <c r="E172" t="s">
         <v>17</v>
@@ -6845,16 +7331,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
+        <v>756</v>
+      </c>
+      <c r="B173" t="s">
         <v>757</v>
       </c>
-      <c r="B173" t="s">
+      <c r="C173" t="s">
         <v>758</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173" t="s">
         <v>759</v>
-      </c>
-      <c r="D173" t="s">
-        <v>760</v>
       </c>
       <c r="E173" t="s">
         <v>10</v>
@@ -6862,16 +7348,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
+        <v>760</v>
+      </c>
+      <c r="B174" t="s">
         <v>761</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
         <v>762</v>
       </c>
-      <c r="C174" t="s">
+      <c r="D174" t="s">
         <v>763</v>
-      </c>
-      <c r="D174" t="s">
-        <v>764</v>
       </c>
       <c r="E174" t="s">
         <v>7</v>
@@ -6879,16 +7365,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
+        <v>764</v>
+      </c>
+      <c r="B175" t="s">
         <v>765</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
         <v>766</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D175" t="s">
         <v>767</v>
-      </c>
-      <c r="D175" t="s">
-        <v>768</v>
       </c>
       <c r="E175" t="s">
         <v>17</v>
@@ -6896,16 +7382,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
+        <v>768</v>
+      </c>
+      <c r="B176" t="s">
         <v>769</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C176" t="s">
         <v>770</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176" t="s">
         <v>771</v>
-      </c>
-      <c r="D176" t="s">
-        <v>772</v>
       </c>
       <c r="E176" t="s">
         <v>10</v>
@@ -6913,16 +7399,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
+        <v>772</v>
+      </c>
+      <c r="B177" t="s">
         <v>773</v>
       </c>
-      <c r="B177" t="s">
+      <c r="C177" t="s">
         <v>774</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177" t="s">
         <v>775</v>
-      </c>
-      <c r="D177" t="s">
-        <v>776</v>
       </c>
       <c r="E177" t="s">
         <v>10</v>
@@ -6930,16 +7416,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
+        <v>776</v>
+      </c>
+      <c r="B178" t="s">
         <v>777</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
         <v>778</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178" t="s">
         <v>779</v>
-      </c>
-      <c r="D178" t="s">
-        <v>780</v>
       </c>
       <c r="E178" t="s">
         <v>7</v>
@@ -6947,16 +7433,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
+        <v>780</v>
+      </c>
+      <c r="B179" t="s">
         <v>781</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
         <v>782</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D179" t="s">
         <v>783</v>
-      </c>
-      <c r="D179" t="s">
-        <v>784</v>
       </c>
       <c r="E179" t="s">
         <v>7</v>
@@ -6964,16 +7450,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
+        <v>784</v>
+      </c>
+      <c r="B180" t="s">
         <v>785</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>786</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
         <v>787</v>
-      </c>
-      <c r="D180" t="s">
-        <v>788</v>
       </c>
       <c r="E180" t="s">
         <v>10</v>
@@ -6981,16 +7467,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
+        <v>788</v>
+      </c>
+      <c r="B181" t="s">
         <v>789</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>790</v>
       </c>
-      <c r="C181" t="s">
+      <c r="D181" t="s">
         <v>791</v>
-      </c>
-      <c r="D181" t="s">
-        <v>792</v>
       </c>
       <c r="E181" t="s">
         <v>17</v>
@@ -6998,16 +7484,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
+        <v>792</v>
+      </c>
+      <c r="B182" t="s">
         <v>793</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C182" t="s">
         <v>794</v>
       </c>
-      <c r="C182" t="s">
+      <c r="D182" t="s">
         <v>795</v>
-      </c>
-      <c r="D182" t="s">
-        <v>796</v>
       </c>
       <c r="E182" t="s">
         <v>7</v>
@@ -7015,16 +7501,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
+        <v>796</v>
+      </c>
+      <c r="B183" t="s">
         <v>797</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>798</v>
       </c>
-      <c r="C183" t="s">
+      <c r="D183" t="s">
         <v>799</v>
-      </c>
-      <c r="D183" t="s">
-        <v>800</v>
       </c>
       <c r="E183" t="s">
         <v>17</v>
@@ -7032,16 +7518,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
+        <v>800</v>
+      </c>
+      <c r="B184" t="s">
         <v>801</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
         <v>802</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D184" t="s">
         <v>803</v>
-      </c>
-      <c r="D184" t="s">
-        <v>804</v>
       </c>
       <c r="E184" t="s">
         <v>7</v>
@@ -7049,16 +7535,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
+        <v>805</v>
+      </c>
+      <c r="B185" t="s">
+        <v>804</v>
+      </c>
+      <c r="C185" t="s">
         <v>806</v>
       </c>
-      <c r="B185" t="s">
-        <v>805</v>
-      </c>
-      <c r="C185" t="s">
+      <c r="D185" t="s">
         <v>807</v>
-      </c>
-      <c r="D185" t="s">
-        <v>808</v>
       </c>
       <c r="E185" t="s">
         <v>10</v>
@@ -7066,13 +7552,13 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
+        <v>808</v>
+      </c>
+      <c r="B186" t="s">
         <v>809</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
         <v>810</v>
-      </c>
-      <c r="C186" t="s">
-        <v>811</v>
       </c>
       <c r="D186" t="s">
         <v>82</v>
@@ -7081,21 +7567,21 @@
         <v>10</v>
       </c>
       <c r="F186" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
+        <v>812</v>
+      </c>
+      <c r="B187" t="s">
         <v>813</v>
       </c>
-      <c r="B187" t="s">
+      <c r="C187" t="s">
         <v>814</v>
       </c>
-      <c r="C187" t="s">
+      <c r="D187" t="s">
         <v>815</v>
-      </c>
-      <c r="D187" t="s">
-        <v>816</v>
       </c>
       <c r="E187" t="s">
         <v>17</v>
@@ -7103,16 +7589,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
+        <v>816</v>
+      </c>
+      <c r="B188" t="s">
         <v>817</v>
       </c>
-      <c r="B188" t="s">
+      <c r="C188" t="s">
         <v>818</v>
       </c>
-      <c r="C188" t="s">
+      <c r="D188" t="s">
         <v>819</v>
-      </c>
-      <c r="D188" t="s">
-        <v>820</v>
       </c>
       <c r="E188" t="s">
         <v>7</v>
@@ -7120,16 +7606,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
+        <v>820</v>
+      </c>
+      <c r="B189" t="s">
         <v>821</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>822</v>
       </c>
-      <c r="C189" t="s">
+      <c r="D189" t="s">
         <v>823</v>
-      </c>
-      <c r="D189" t="s">
-        <v>824</v>
       </c>
       <c r="E189" t="s">
         <v>17</v>
@@ -7137,16 +7623,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
+        <v>824</v>
+      </c>
+      <c r="B190" t="s">
         <v>825</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C190" t="s">
         <v>826</v>
       </c>
-      <c r="C190" t="s">
+      <c r="D190" t="s">
         <v>827</v>
-      </c>
-      <c r="D190" t="s">
-        <v>828</v>
       </c>
       <c r="E190" t="s">
         <v>7</v>
@@ -7154,16 +7640,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
+        <v>828</v>
+      </c>
+      <c r="B191" t="s">
         <v>829</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
         <v>830</v>
       </c>
-      <c r="C191" t="s">
+      <c r="D191" t="s">
         <v>831</v>
-      </c>
-      <c r="D191" t="s">
-        <v>832</v>
       </c>
       <c r="E191" t="s">
         <v>17</v>
@@ -7171,16 +7657,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
+        <v>832</v>
+      </c>
+      <c r="B192" t="s">
         <v>833</v>
       </c>
-      <c r="B192" t="s">
+      <c r="C192" t="s">
         <v>834</v>
       </c>
-      <c r="C192" t="s">
+      <c r="D192" t="s">
         <v>835</v>
-      </c>
-      <c r="D192" t="s">
-        <v>836</v>
       </c>
       <c r="E192" t="s">
         <v>17</v>
@@ -7188,16 +7674,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
+        <v>836</v>
+      </c>
+      <c r="B193" t="s">
         <v>837</v>
       </c>
-      <c r="B193" t="s">
+      <c r="C193" t="s">
         <v>838</v>
       </c>
-      <c r="C193" t="s">
+      <c r="D193" t="s">
         <v>839</v>
-      </c>
-      <c r="D193" t="s">
-        <v>840</v>
       </c>
       <c r="E193" t="s">
         <v>17</v>
@@ -7205,16 +7691,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
+        <v>840</v>
+      </c>
+      <c r="B194" t="s">
         <v>841</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C194" t="s">
         <v>842</v>
       </c>
-      <c r="C194" t="s">
+      <c r="D194" t="s">
         <v>843</v>
-      </c>
-      <c r="D194" t="s">
-        <v>844</v>
       </c>
       <c r="E194" t="s">
         <v>10</v>
@@ -7222,16 +7708,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
+        <v>844</v>
+      </c>
+      <c r="B195" t="s">
         <v>845</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" t="s">
         <v>846</v>
       </c>
-      <c r="C195" t="s">
+      <c r="D195" t="s">
         <v>847</v>
-      </c>
-      <c r="D195" t="s">
-        <v>848</v>
       </c>
       <c r="E195" t="s">
         <v>10</v>
@@ -7239,16 +7725,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
+        <v>848</v>
+      </c>
+      <c r="B196" t="s">
         <v>849</v>
       </c>
-      <c r="B196" t="s">
+      <c r="C196" t="s">
         <v>850</v>
       </c>
-      <c r="C196" t="s">
+      <c r="D196" t="s">
         <v>851</v>
-      </c>
-      <c r="D196" t="s">
-        <v>852</v>
       </c>
       <c r="E196" t="s">
         <v>17</v>
@@ -7256,16 +7742,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
+        <v>852</v>
+      </c>
+      <c r="B197" t="s">
         <v>853</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C197" t="s">
         <v>854</v>
       </c>
-      <c r="C197" t="s">
+      <c r="D197" t="s">
         <v>855</v>
-      </c>
-      <c r="D197" t="s">
-        <v>856</v>
       </c>
       <c r="E197" t="s">
         <v>10</v>
@@ -7273,16 +7759,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
+        <v>856</v>
+      </c>
+      <c r="B198" t="s">
         <v>857</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C198" t="s">
         <v>858</v>
       </c>
-      <c r="C198" t="s">
+      <c r="D198" t="s">
         <v>859</v>
-      </c>
-      <c r="D198" t="s">
-        <v>860</v>
       </c>
       <c r="E198" t="s">
         <v>10</v>
@@ -7290,16 +7776,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
+        <v>860</v>
+      </c>
+      <c r="B199" t="s">
         <v>861</v>
       </c>
-      <c r="B199" t="s">
+      <c r="C199" t="s">
         <v>862</v>
       </c>
-      <c r="C199" t="s">
+      <c r="D199" t="s">
         <v>863</v>
-      </c>
-      <c r="D199" t="s">
-        <v>864</v>
       </c>
       <c r="E199" t="s">
         <v>10</v>
@@ -7307,10 +7793,10 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
+        <v>864</v>
+      </c>
+      <c r="B200" t="s">
         <v>865</v>
-      </c>
-      <c r="B200" t="s">
-        <v>866</v>
       </c>
       <c r="C200" t="s">
         <v>82</v>
@@ -7324,36 +7810,36 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
+        <v>866</v>
+      </c>
+      <c r="B201" t="s">
         <v>867</v>
       </c>
-      <c r="B201" t="s">
+      <c r="C201" t="s">
         <v>868</v>
       </c>
-      <c r="C201" t="s">
+      <c r="D201" t="s">
         <v>869</v>
       </c>
-      <c r="D201" t="s">
+      <c r="E201" t="s">
+        <v>7</v>
+      </c>
+      <c r="F201" t="s">
         <v>870</v>
-      </c>
-      <c r="E201" t="s">
-        <v>7</v>
-      </c>
-      <c r="F201" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
+        <v>871</v>
+      </c>
+      <c r="B202" t="s">
         <v>872</v>
       </c>
-      <c r="B202" t="s">
+      <c r="C202" t="s">
         <v>873</v>
       </c>
-      <c r="C202" t="s">
+      <c r="D202" t="s">
         <v>874</v>
-      </c>
-      <c r="D202" t="s">
-        <v>875</v>
       </c>
       <c r="E202" t="s">
         <v>7</v>
@@ -7361,16 +7847,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B203" t="s">
         <v>485</v>
       </c>
       <c r="C203" t="s">
+        <v>876</v>
+      </c>
+      <c r="D203" t="s">
         <v>877</v>
-      </c>
-      <c r="D203" t="s">
-        <v>878</v>
       </c>
       <c r="E203" t="s">
         <v>7</v>
@@ -7378,56 +7864,56 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
+        <v>878</v>
+      </c>
+      <c r="B204" t="s">
         <v>879</v>
       </c>
-      <c r="B204" t="s">
+      <c r="C204" t="s">
         <v>880</v>
       </c>
-      <c r="C204" t="s">
+      <c r="D204" t="s">
         <v>881</v>
       </c>
-      <c r="D204" t="s">
+      <c r="E204" t="s">
+        <v>7</v>
+      </c>
+      <c r="F204" t="s">
         <v>882</v>
-      </c>
-      <c r="E204" t="s">
-        <v>7</v>
-      </c>
-      <c r="F204" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
+        <v>883</v>
+      </c>
+      <c r="B205" t="s">
         <v>884</v>
       </c>
-      <c r="B205" t="s">
+      <c r="C205" t="s">
         <v>885</v>
       </c>
-      <c r="C205" t="s">
+      <c r="D205" t="s">
         <v>886</v>
       </c>
-      <c r="D205" t="s">
+      <c r="E205" t="s">
+        <v>17</v>
+      </c>
+      <c r="F205" t="s">
         <v>887</v>
-      </c>
-      <c r="E205" t="s">
-        <v>17</v>
-      </c>
-      <c r="F205" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
+        <v>888</v>
+      </c>
+      <c r="B206" t="s">
         <v>889</v>
       </c>
-      <c r="B206" t="s">
+      <c r="C206" t="s">
         <v>890</v>
       </c>
-      <c r="C206" t="s">
+      <c r="D206" t="s">
         <v>891</v>
-      </c>
-      <c r="D206" t="s">
-        <v>892</v>
       </c>
       <c r="E206" t="s">
         <v>7</v>
@@ -7435,16 +7921,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
+        <v>892</v>
+      </c>
+      <c r="B207" t="s">
         <v>893</v>
       </c>
-      <c r="B207" t="s">
+      <c r="C207" t="s">
         <v>894</v>
       </c>
-      <c r="C207" t="s">
+      <c r="D207" t="s">
         <v>895</v>
-      </c>
-      <c r="D207" t="s">
-        <v>896</v>
       </c>
       <c r="E207" t="s">
         <v>17</v>
@@ -7452,16 +7938,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
+        <v>896</v>
+      </c>
+      <c r="B208" t="s">
         <v>897</v>
       </c>
-      <c r="B208" t="s">
+      <c r="C208" t="s">
         <v>898</v>
       </c>
-      <c r="C208" t="s">
+      <c r="D208" t="s">
         <v>899</v>
-      </c>
-      <c r="D208" t="s">
-        <v>900</v>
       </c>
       <c r="E208" t="s">
         <v>17</v>
@@ -7469,36 +7955,36 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
+        <v>900</v>
+      </c>
+      <c r="B209" t="s">
         <v>901</v>
       </c>
-      <c r="B209" t="s">
+      <c r="C209" t="s">
         <v>902</v>
       </c>
-      <c r="C209" t="s">
+      <c r="D209" t="s">
         <v>903</v>
-      </c>
-      <c r="D209" t="s">
-        <v>904</v>
       </c>
       <c r="E209" t="s">
         <v>10</v>
       </c>
       <c r="F209" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
+        <v>905</v>
+      </c>
+      <c r="B210" t="s">
         <v>906</v>
       </c>
-      <c r="B210" t="s">
+      <c r="C210" t="s">
         <v>907</v>
       </c>
-      <c r="C210" t="s">
+      <c r="D210" t="s">
         <v>908</v>
-      </c>
-      <c r="D210" t="s">
-        <v>909</v>
       </c>
       <c r="E210" t="s">
         <v>17</v>
@@ -7506,16 +7992,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
+        <v>909</v>
+      </c>
+      <c r="B211" t="s">
         <v>910</v>
       </c>
-      <c r="B211" t="s">
+      <c r="C211" t="s">
         <v>911</v>
       </c>
-      <c r="C211" t="s">
+      <c r="D211" t="s">
         <v>912</v>
-      </c>
-      <c r="D211" t="s">
-        <v>913</v>
       </c>
       <c r="E211" t="s">
         <v>7</v>
@@ -7523,16 +8009,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
+        <v>913</v>
+      </c>
+      <c r="B212" t="s">
         <v>914</v>
       </c>
-      <c r="B212" t="s">
+      <c r="C212" t="s">
         <v>915</v>
       </c>
-      <c r="C212" t="s">
+      <c r="D212" t="s">
         <v>916</v>
-      </c>
-      <c r="D212" t="s">
-        <v>917</v>
       </c>
       <c r="E212" t="s">
         <v>7</v>
@@ -7540,16 +8026,16 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
+        <v>917</v>
+      </c>
+      <c r="B213" t="s">
         <v>918</v>
       </c>
-      <c r="B213" t="s">
+      <c r="C213" t="s">
         <v>919</v>
       </c>
-      <c r="C213" t="s">
+      <c r="D213" t="s">
         <v>920</v>
-      </c>
-      <c r="D213" t="s">
-        <v>921</v>
       </c>
       <c r="E213" t="s">
         <v>7</v>
@@ -7557,16 +8043,16 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
+        <v>921</v>
+      </c>
+      <c r="B214" t="s">
         <v>922</v>
       </c>
-      <c r="B214" t="s">
+      <c r="C214" t="s">
         <v>923</v>
       </c>
-      <c r="C214" t="s">
+      <c r="D214" t="s">
         <v>924</v>
-      </c>
-      <c r="D214" t="s">
-        <v>925</v>
       </c>
       <c r="E214" t="s">
         <v>10</v>
@@ -7574,16 +8060,16 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
+        <v>925</v>
+      </c>
+      <c r="B215" t="s">
         <v>926</v>
       </c>
-      <c r="B215" t="s">
+      <c r="C215" t="s">
         <v>927</v>
       </c>
-      <c r="C215" t="s">
+      <c r="D215" t="s">
         <v>928</v>
-      </c>
-      <c r="D215" t="s">
-        <v>929</v>
       </c>
       <c r="E215" t="s">
         <v>10</v>
@@ -7591,36 +8077,36 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
+        <v>929</v>
+      </c>
+      <c r="B216" t="s">
         <v>930</v>
       </c>
-      <c r="B216" t="s">
+      <c r="C216" t="s">
         <v>931</v>
       </c>
-      <c r="C216" t="s">
+      <c r="D216" t="s">
         <v>932</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E216" t="s">
+        <v>17</v>
+      </c>
+      <c r="F216" t="s">
         <v>933</v>
-      </c>
-      <c r="E216" t="s">
-        <v>17</v>
-      </c>
-      <c r="F216" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
+        <v>934</v>
+      </c>
+      <c r="B217" t="s">
         <v>935</v>
       </c>
-      <c r="B217" t="s">
+      <c r="C217" t="s">
         <v>936</v>
       </c>
-      <c r="C217" t="s">
+      <c r="D217" t="s">
         <v>937</v>
-      </c>
-      <c r="D217" t="s">
-        <v>938</v>
       </c>
       <c r="E217" t="s">
         <v>10</v>
@@ -7628,16 +8114,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
+        <v>938</v>
+      </c>
+      <c r="B218" t="s">
         <v>939</v>
       </c>
-      <c r="B218" t="s">
+      <c r="C218" t="s">
         <v>940</v>
       </c>
-      <c r="C218" t="s">
+      <c r="D218" t="s">
         <v>941</v>
-      </c>
-      <c r="D218" t="s">
-        <v>942</v>
       </c>
       <c r="E218" t="s">
         <v>10</v>
@@ -7645,16 +8131,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
+        <v>942</v>
+      </c>
+      <c r="B219" t="s">
         <v>943</v>
       </c>
-      <c r="B219" t="s">
+      <c r="C219" t="s">
         <v>944</v>
       </c>
-      <c r="C219" t="s">
+      <c r="D219" t="s">
         <v>945</v>
-      </c>
-      <c r="D219" t="s">
-        <v>946</v>
       </c>
       <c r="E219" t="s">
         <v>10</v>
@@ -7662,33 +8148,33 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
+        <v>946</v>
+      </c>
+      <c r="B220" t="s">
         <v>947</v>
       </c>
-      <c r="B220" t="s">
+      <c r="C220" t="s">
         <v>948</v>
       </c>
-      <c r="C220" t="s">
+      <c r="D220" t="s">
         <v>949</v>
       </c>
-      <c r="D220" t="s">
+      <c r="E220" t="s">
+        <v>17</v>
+      </c>
+      <c r="F220" t="s">
         <v>950</v>
-      </c>
-      <c r="E220" t="s">
-        <v>17</v>
-      </c>
-      <c r="F220" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
+        <v>951</v>
+      </c>
+      <c r="B221" t="s">
         <v>952</v>
       </c>
-      <c r="B221" t="s">
+      <c r="C221" t="s">
         <v>953</v>
-      </c>
-      <c r="C221" t="s">
-        <v>954</v>
       </c>
       <c r="D221" t="s">
         <v>139</v>
@@ -7699,16 +8185,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
+        <v>954</v>
+      </c>
+      <c r="B222" t="s">
         <v>955</v>
       </c>
-      <c r="B222" t="s">
+      <c r="C222" t="s">
         <v>956</v>
       </c>
-      <c r="C222" t="s">
+      <c r="D222" t="s">
         <v>957</v>
-      </c>
-      <c r="D222" t="s">
-        <v>958</v>
       </c>
       <c r="E222" t="s">
         <v>10</v>
@@ -7716,16 +8202,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B223" t="s">
         <v>71</v>
       </c>
       <c r="C223" t="s">
+        <v>959</v>
+      </c>
+      <c r="D223" t="s">
         <v>960</v>
-      </c>
-      <c r="D223" t="s">
-        <v>961</v>
       </c>
       <c r="E223" t="s">
         <v>7</v>
@@ -7733,90 +8219,90 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
+        <v>961</v>
+      </c>
+      <c r="B224" t="s">
         <v>962</v>
       </c>
-      <c r="B224" t="s">
+      <c r="C224" t="s">
         <v>963</v>
       </c>
-      <c r="C224" t="s">
+      <c r="D224" t="s">
         <v>964</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
+        <v>17</v>
+      </c>
+      <c r="F224" t="s">
         <v>965</v>
-      </c>
-      <c r="E224" t="s">
-        <v>17</v>
-      </c>
-      <c r="F224" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
+        <v>966</v>
+      </c>
+      <c r="B225" t="s">
         <v>967</v>
       </c>
-      <c r="B225" t="s">
+      <c r="C225" t="s">
         <v>968</v>
       </c>
-      <c r="C225" t="s">
+      <c r="D225" t="s">
         <v>969</v>
       </c>
-      <c r="D225" t="s">
+      <c r="E225" t="s">
+        <v>17</v>
+      </c>
+      <c r="F225" t="s">
         <v>970</v>
-      </c>
-      <c r="E225" t="s">
-        <v>17</v>
-      </c>
-      <c r="F225" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
+        <v>971</v>
+      </c>
+      <c r="B226" t="s">
         <v>972</v>
       </c>
-      <c r="B226" t="s">
+      <c r="C226" t="s">
         <v>973</v>
       </c>
-      <c r="C226" t="s">
+      <c r="D226" t="s">
         <v>974</v>
       </c>
-      <c r="D226" t="s">
+      <c r="E226" t="s">
+        <v>17</v>
+      </c>
+      <c r="F226" t="s">
         <v>975</v>
-      </c>
-      <c r="E226" t="s">
-        <v>17</v>
-      </c>
-      <c r="F226" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B227" t="s">
         <v>82</v>
       </c>
       <c r="C227" t="s">
+        <v>977</v>
+      </c>
+      <c r="D227" t="s">
         <v>978</v>
-      </c>
-      <c r="D227" t="s">
-        <v>979</v>
       </c>
       <c r="E227" t="s">
         <v>10</v>
       </c>
       <c r="F227" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
+        <v>980</v>
+      </c>
+      <c r="B228" t="s">
         <v>981</v>
-      </c>
-      <c r="B228" t="s">
-        <v>982</v>
       </c>
       <c r="C228" t="s">
         <v>82</v>
@@ -7828,101 +8314,101 @@
         <v>17</v>
       </c>
       <c r="F228" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
+        <v>983</v>
+      </c>
+      <c r="B229" t="s">
         <v>984</v>
       </c>
-      <c r="B229" t="s">
+      <c r="C229" t="s">
         <v>985</v>
       </c>
-      <c r="C229" t="s">
+      <c r="D229" t="s">
         <v>986</v>
       </c>
-      <c r="D229" t="s">
+      <c r="E229" t="s">
+        <v>17</v>
+      </c>
+      <c r="F229" t="s">
         <v>987</v>
-      </c>
-      <c r="E229" t="s">
-        <v>17</v>
-      </c>
-      <c r="F229" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B230" t="s">
         <v>82</v>
       </c>
       <c r="C230" t="s">
+        <v>989</v>
+      </c>
+      <c r="D230" t="s">
         <v>990</v>
-      </c>
-      <c r="D230" t="s">
-        <v>991</v>
       </c>
       <c r="E230" t="s">
         <v>10</v>
       </c>
       <c r="F230" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
+        <v>992</v>
+      </c>
+      <c r="B231" t="s">
         <v>993</v>
       </c>
-      <c r="B231" t="s">
+      <c r="C231" t="s">
         <v>994</v>
       </c>
-      <c r="C231" t="s">
+      <c r="D231" t="s">
         <v>995</v>
       </c>
-      <c r="D231" t="s">
+      <c r="E231" t="s">
+        <v>7</v>
+      </c>
+      <c r="F231" t="s">
         <v>996</v>
-      </c>
-      <c r="E231" t="s">
-        <v>7</v>
-      </c>
-      <c r="F231" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
+        <v>997</v>
+      </c>
+      <c r="B232" t="s">
         <v>998</v>
       </c>
-      <c r="B232" t="s">
+      <c r="C232" t="s">
         <v>999</v>
       </c>
-      <c r="C232" t="s">
+      <c r="D232" t="s">
         <v>1000</v>
-      </c>
-      <c r="D232" t="s">
-        <v>1001</v>
       </c>
       <c r="E232" t="s">
         <v>10</v>
       </c>
       <c r="F232" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B233" t="s">
         <v>1003</v>
       </c>
-      <c r="B233" t="s">
+      <c r="C233" t="s">
         <v>1004</v>
       </c>
-      <c r="C233" t="s">
+      <c r="D233" t="s">
         <v>1005</v>
-      </c>
-      <c r="D233" t="s">
-        <v>1006</v>
       </c>
       <c r="E233" t="s">
         <v>10</v>
@@ -7930,16 +8416,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B234" t="s">
         <v>1007</v>
       </c>
-      <c r="B234" t="s">
+      <c r="C234" t="s">
         <v>1008</v>
       </c>
-      <c r="C234" t="s">
+      <c r="D234" t="s">
         <v>1009</v>
-      </c>
-      <c r="D234" t="s">
-        <v>1010</v>
       </c>
       <c r="E234" t="s">
         <v>10</v>
@@ -7947,16 +8433,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B235" t="s">
         <v>1011</v>
       </c>
-      <c r="B235" t="s">
+      <c r="C235" t="s">
         <v>1012</v>
       </c>
-      <c r="C235" t="s">
+      <c r="D235" t="s">
         <v>1013</v>
-      </c>
-      <c r="D235" t="s">
-        <v>1014</v>
       </c>
       <c r="E235" t="s">
         <v>17</v>
@@ -7964,16 +8450,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B236" t="s">
         <v>1015</v>
       </c>
-      <c r="B236" t="s">
+      <c r="C236" t="s">
         <v>1016</v>
       </c>
-      <c r="C236" t="s">
+      <c r="D236" t="s">
         <v>1017</v>
-      </c>
-      <c r="D236" t="s">
-        <v>1018</v>
       </c>
       <c r="E236" t="s">
         <v>17</v>
@@ -7981,16 +8467,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B237" t="s">
         <v>1019</v>
       </c>
-      <c r="B237" t="s">
+      <c r="C237" t="s">
         <v>1020</v>
       </c>
-      <c r="C237" t="s">
+      <c r="D237" t="s">
         <v>1021</v>
-      </c>
-      <c r="D237" t="s">
-        <v>1022</v>
       </c>
       <c r="E237" t="s">
         <v>17</v>
@@ -7998,16 +8484,16 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B238" t="s">
         <v>1023</v>
       </c>
-      <c r="B238" t="s">
+      <c r="C238" t="s">
         <v>1024</v>
       </c>
-      <c r="C238" t="s">
+      <c r="D238" t="s">
         <v>1025</v>
-      </c>
-      <c r="D238" t="s">
-        <v>1026</v>
       </c>
       <c r="E238" t="s">
         <v>10</v>
@@ -8015,16 +8501,16 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B239" t="s">
         <v>1027</v>
       </c>
-      <c r="B239" t="s">
+      <c r="C239" t="s">
         <v>1028</v>
       </c>
-      <c r="C239" t="s">
+      <c r="D239" t="s">
         <v>1029</v>
-      </c>
-      <c r="D239" t="s">
-        <v>1030</v>
       </c>
       <c r="E239" t="s">
         <v>17</v>
@@ -8032,16 +8518,16 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B240" t="s">
         <v>71</v>
       </c>
       <c r="C240" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D240" t="s">
         <v>1032</v>
-      </c>
-      <c r="D240" t="s">
-        <v>1033</v>
       </c>
       <c r="E240" t="s">
         <v>10</v>
@@ -8049,16 +8535,16 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B241" t="s">
         <v>1034</v>
       </c>
-      <c r="B241" t="s">
+      <c r="C241" t="s">
         <v>1035</v>
       </c>
-      <c r="C241" t="s">
+      <c r="D241" t="s">
         <v>1036</v>
-      </c>
-      <c r="D241" t="s">
-        <v>1037</v>
       </c>
       <c r="E241" t="s">
         <v>7</v>
@@ -8066,16 +8552,16 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B242" t="s">
         <v>1038</v>
       </c>
-      <c r="B242" t="s">
+      <c r="C242" t="s">
         <v>1039</v>
       </c>
-      <c r="C242" t="s">
+      <c r="D242" t="s">
         <v>1040</v>
-      </c>
-      <c r="D242" t="s">
-        <v>1041</v>
       </c>
       <c r="E242" t="s">
         <v>10</v>
@@ -8083,16 +8569,16 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B243" t="s">
         <v>1042</v>
       </c>
-      <c r="B243" t="s">
+      <c r="C243" t="s">
         <v>1043</v>
       </c>
-      <c r="C243" t="s">
+      <c r="D243" t="s">
         <v>1044</v>
-      </c>
-      <c r="D243" t="s">
-        <v>1045</v>
       </c>
       <c r="E243" t="s">
         <v>17</v>
@@ -8100,13 +8586,13 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B244" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C244" t="s">
         <v>1046</v>
-      </c>
-      <c r="C244" t="s">
-        <v>1047</v>
       </c>
       <c r="D244" t="s">
         <v>71</v>
@@ -8117,16 +8603,16 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B245" t="s">
         <v>71</v>
       </c>
       <c r="C245" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D245" t="s">
         <v>1049</v>
-      </c>
-      <c r="D245" t="s">
-        <v>1050</v>
       </c>
       <c r="E245" t="s">
         <v>10</v>
@@ -8134,37 +8620,788 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B246" t="s">
         <v>1051</v>
       </c>
-      <c r="B246" t="s">
+      <c r="C246" t="s">
         <v>1052</v>
       </c>
-      <c r="C246" t="s">
+      <c r="D246" t="s">
         <v>1053</v>
-      </c>
-      <c r="D246" t="s">
-        <v>1054</v>
       </c>
       <c r="E246" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A286"/>
-      <c r="B286"/>
-      <c r="C286"/>
-      <c r="D286"/>
-      <c r="E286"/>
-    </row>
-    <row r="292" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A292"/>
-      <c r="B292"/>
-      <c r="C292"/>
-      <c r="D292"/>
-      <c r="E292"/>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B247" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C247" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D247" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E247" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C248" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D248" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E248" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C249" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D249" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E249" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B250" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C250" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D250" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E250" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B251" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C251" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D251" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E251" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C252" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D252" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E252" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C253" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D253" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E253" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C254" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D254" t="s">
+        <v>209</v>
+      </c>
+      <c r="E254" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A255" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C255" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D255" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E255" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A256" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B256" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C256" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D256" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E256" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C257" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D257" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E257" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C258" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D258" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E258" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C259" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D259" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E259" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C260" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D260" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E260" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B261" t="s">
+        <v>209</v>
+      </c>
+      <c r="C261" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D261" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E261" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B262" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C262" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D262" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E262" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B263" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C263" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D263" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E263" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B264" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C264" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D264" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E264" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B265" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C265" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D265" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E265" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B266" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C266" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D266" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E266" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B267" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C267" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D267" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E267" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B268" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C268" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D268" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E268" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B269" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C269" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D269" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E269" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B270" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C270" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D270" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E270" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B271" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C271" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D271" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E271" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B272" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C272" t="s">
+        <v>210</v>
+      </c>
+      <c r="D272" t="s">
+        <v>209</v>
+      </c>
+      <c r="E272" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B273" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C273" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D273" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E273" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B274" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C274" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D274" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E274" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B275" t="s">
+        <v>620</v>
+      </c>
+      <c r="C275" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D275" t="s">
+        <v>514</v>
+      </c>
+      <c r="E275" t="s">
+        <v>10</v>
+      </c>
+      <c r="F275" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B276" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C276" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D276" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E276" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B277" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C277" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D277" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E277" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B278" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C278" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D278" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E278" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B279" t="s">
+        <v>210</v>
+      </c>
+      <c r="C279" t="s">
+        <v>209</v>
+      </c>
+      <c r="D279" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E279" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B280" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C280" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D280" t="s">
+        <v>209</v>
+      </c>
+      <c r="E280" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B281" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C281" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D281" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E281" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B282" t="s">
+        <v>209</v>
+      </c>
+      <c r="C282" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D282" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E282" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B283" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C283" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D283" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E283" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B284" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C284" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D284" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E284" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B285" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C285" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E285" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B286" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C286" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D286" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E286" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B287" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C287" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D287" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E287" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B288" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C288" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D288" t="s">
+        <v>209</v>
+      </c>
+      <c r="E288" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B289" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C289" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D289" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E289" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B290" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C290" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D290" t="s">
+        <v>82</v>
+      </c>
+      <c r="E290" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A327"/>
+      <c r="B327"/>
+      <c r="C327"/>
+      <c r="D327"/>
+      <c r="E327"/>
+    </row>
+    <row r="333" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A333"/>
+      <c r="B333"/>
+      <c r="C333"/>
+      <c r="D333"/>
+      <c r="E333"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E452" xr:uid="{AA7778BF-C4D9-8B46-A8CD-4B3F292AD9D0}"/>
+  <autoFilter ref="A1:E493" xr:uid="{AA7778BF-C4D9-8B46-A8CD-4B3F292AD9D0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datos/Practica Test.xlsx
+++ b/datos/Practica Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorge/Desktop/AUTOESCUELA/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82C9AC5-3DC6-F042-9908-AD03F2AA172F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2DE6B3-C7F9-C84D-8F20-FCAD789931C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="23220" windowHeight="16820" xr2:uid="{AE6512D7-AD52-4543-8CDE-87DCF5042393}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="T20" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20'!$A$1:$E$493</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20'!$A$1:$E$514</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="1218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="1300">
   <si>
     <t>Pregunta</t>
   </si>
@@ -3693,6 +3693,252 @@
   </si>
   <si>
     <t>¿Cómo debemos proteger el cuello para evitar movimientos bruscos que pudieran perjudicar al herido?</t>
+  </si>
+  <si>
+    <t>¿Está permitido estacionar en una intersección?</t>
+  </si>
+  <si>
+    <t>¿Cuántas horas necesita dormir una persona para que el descanso se considere adecuado?</t>
+  </si>
+  <si>
+    <t>¿Qué debe hacer si está conduciendo y está muy cansado o fatigado?</t>
+  </si>
+  <si>
+    <t>¿Qué es lo primero que hay que hacer con un herido hasta que llegue la ayuda sanitaria?</t>
+  </si>
+  <si>
+    <t>El alcohol se elimina...</t>
+  </si>
+  <si>
+    <t>¿Se considera desplazamiento lateral la corrección de trayectoria en el mismo carril en el que se circula?</t>
+  </si>
+  <si>
+    <t>¿Está permitida la circulación de vehículos si el silenciador está estropeado y, por tanto no cumple su función con eficacia?</t>
+  </si>
+  <si>
+    <t>¿Qué significado tienen las señales verticales circulares de color azul?</t>
+  </si>
+  <si>
+    <t>¿Qué luz debemos encender tanto de día como de noche cuando cae nieve?</t>
+  </si>
+  <si>
+    <t>La depresión, ¿qué efectos tiene en la conducción?</t>
+  </si>
+  <si>
+    <t>¿Cómo deben ser las luces en un vehículo prioritario?</t>
+  </si>
+  <si>
+    <t>¿Cuántos segundos tras las insuflaciones debemos esperar para considerar que el herido está en parada cardíaca?</t>
+  </si>
+  <si>
+    <t>¿Se puede circular marcha atrás en una autopista?</t>
+  </si>
+  <si>
+    <t>Desde el anochecer hasta el amanecer, ¿qué luces son obligatorias?</t>
+  </si>
+  <si>
+    <t>¿Deben los vehículos especiales agrícolas llevar placa de matrícula trasera?</t>
+  </si>
+  <si>
+    <t>¿Por dónde debe circular un ciclomotor en esta vía?</t>
+  </si>
+  <si>
+    <t>imagenes/260820B.png</t>
+  </si>
+  <si>
+    <t>¿Qué es obligatorio cuando tenga que realizar la maniobra de marcha atrás?</t>
+  </si>
+  <si>
+    <t>Es más seguro colocar un dispositivo de retención infantil en…</t>
+  </si>
+  <si>
+    <t>¿De qué depende la peligrosidad en una maniobra de adelantamiento?</t>
+  </si>
+  <si>
+    <t>¿Cuándo tiene que encender una motocicleta el alumbrado de corto alcance durante el día?</t>
+  </si>
+  <si>
+    <t>¿Están obligadas a llevar la luz de largo alcance las motocicletas con una cilindrada que no supere los 125 centímetros cúbicos?</t>
+  </si>
+  <si>
+    <t>Circula de noche con las luces largas encendidas. Ve peatones en el arcén. ¿Está obligado a cambiar la luz la larga por la corta?</t>
+  </si>
+  <si>
+    <t>De 7 a 9 horas.</t>
+  </si>
+  <si>
+    <t>Tomar una bebida alcohólica.</t>
+  </si>
+  <si>
+    <t>Comprobar y mantener su respiración</t>
+  </si>
+  <si>
+    <t>Más rápido cuando dormimos.</t>
+  </si>
+  <si>
+    <t>Sí, pero solo puede circular por vías interurbanas.</t>
+  </si>
+  <si>
+    <t>Prohibición</t>
+  </si>
+  <si>
+    <t>Luces de emergencia</t>
+  </si>
+  <si>
+    <t>Ninguno.</t>
+  </si>
+  <si>
+    <t>Luces fijas en la parte superior del vehículo.</t>
+  </si>
+  <si>
+    <t>30 segundos</t>
+  </si>
+  <si>
+    <t>La luz de posición solamente.</t>
+  </si>
+  <si>
+    <t>Únicamente aquellos vehículos con MMA superior a 3000 kg</t>
+  </si>
+  <si>
+    <t>Por la calzada, lo más cerca posible del borde derecho.</t>
+  </si>
+  <si>
+    <t>Hacerlo lentamente, señalizar la maniobra y asegurarse, incluso llegando a bajar del vehículo, de que no supone peligro.</t>
+  </si>
+  <si>
+    <t>el asiento del copiloto para que el conductor lo vigile.</t>
+  </si>
+  <si>
+    <t>De la vía donde se efectúa</t>
+  </si>
+  <si>
+    <t>Solamente si conduce por un túnel y en tramos que son afectados por la señal vertical de túnel.</t>
+  </si>
+  <si>
+    <t>Sí, si tienen sidecar. En el caso contrario, no.</t>
+  </si>
+  <si>
+    <t>No es necesario.</t>
+  </si>
+  <si>
+    <t>Solo si se dejan encendidas las luces de emergencia.</t>
+  </si>
+  <si>
+    <t>De 10 a 12 horas.</t>
+  </si>
+  <si>
+    <t>Tomar una bebida estimulante (té, café)</t>
+  </si>
+  <si>
+    <t>Comprobar si tiene hemorragia.</t>
+  </si>
+  <si>
+    <t>Más lento cuando dormimos.</t>
+  </si>
+  <si>
+    <t>Únicamente cuando lo realizan los camiones</t>
+  </si>
+  <si>
+    <t>No, debido a la contaminación acústica que produce.</t>
+  </si>
+  <si>
+    <t>Obligación</t>
+  </si>
+  <si>
+    <t>Luz de largo alcance</t>
+  </si>
+  <si>
+    <t>Ansiedad e impulsividad.</t>
+  </si>
+  <si>
+    <t>Luces intermitentes o giratorias.</t>
+  </si>
+  <si>
+    <t>45 segundos</t>
+  </si>
+  <si>
+    <t>Sí, si está dentro de poblado.</t>
+  </si>
+  <si>
+    <t>La luz de posición y el alumbrado antiniebla.</t>
+  </si>
+  <si>
+    <t>Como no tiene arcén, los ciclomotores no pueden circular.</t>
+  </si>
+  <si>
+    <t>Hacerla lentamente, señalizar la maniobra y encender las luces de emergencia.</t>
+  </si>
+  <si>
+    <t>cualquiera de los asientos laterales, porque el respaldo de los asientos delanteros lo protegerá.</t>
+  </si>
+  <si>
+    <t>Del tipo de vehículos que la realicen</t>
+  </si>
+  <si>
+    <t>Solamente si conduce de noche o en condiciones meteorológicas desfavorables.</t>
+  </si>
+  <si>
+    <t>Sí, una o dos luces.</t>
+  </si>
+  <si>
+    <t>Sí, para no deslumbrar.</t>
+  </si>
+  <si>
+    <t>No, cuando se impida el giro a otros vehículos.</t>
+  </si>
+  <si>
+    <t>De 3 a 4 horas.</t>
+  </si>
+  <si>
+    <t>Detener el vehículo para descansar o dormir.</t>
+  </si>
+  <si>
+    <t>Limpiar las heridas con agua.</t>
+  </si>
+  <si>
+    <t>Igual de rápido estando despierto que dormido.</t>
+  </si>
+  <si>
+    <t>No, excepto las motocicletas, que no necesitan silenciador.</t>
+  </si>
+  <si>
+    <t>Precaución</t>
+  </si>
+  <si>
+    <t>Luz de corto alcance</t>
+  </si>
+  <si>
+    <t>Distracciones y somnolencia.</t>
+  </si>
+  <si>
+    <t>Luces intermitentes que se apaguen automáticamente cada 5 minutos.</t>
+  </si>
+  <si>
+    <t>10 segundos</t>
+  </si>
+  <si>
+    <t>Sí, pero sin obstaculizar.</t>
+  </si>
+  <si>
+    <t>La luz de posición con las de corto o largo alcance, dependiendo de las circunstancias.</t>
+  </si>
+  <si>
+    <t>Por el centro del carril derecho para que los demás usuarios de la vía puedan verle.</t>
+  </si>
+  <si>
+    <t>Mirar hacia atrás girando el cuerpo y apoyando el antebrazo en el asiento del acompañante, y tocar el claxon.</t>
+  </si>
+  <si>
+    <t>el asiento trasero central porque es el menos afectado en los impactos laterales.</t>
+  </si>
+  <si>
+    <t>De la velocidad a la que se realiza.</t>
+  </si>
+  <si>
+    <t>Cuando conduce en cualquier vía pública.</t>
+  </si>
+  <si>
+    <t>Sí, pero solamente en los tramos rectos.</t>
   </si>
 </sst>
 </file>
@@ -4086,7 +4332,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7778BF-C4D9-8B46-A8CD-4B3F292AD9D0}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:F333"/>
+  <dimension ref="A1:F354"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.5" bestFit="1" customWidth="1"/>
@@ -9386,22 +9632,399 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A327"/>
-      <c r="B327"/>
-      <c r="C327"/>
-      <c r="D327"/>
-      <c r="E327"/>
-    </row>
-    <row r="333" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A333"/>
-      <c r="B333"/>
-      <c r="C333"/>
-      <c r="D333"/>
-      <c r="E333"/>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B291" t="s">
+        <v>604</v>
+      </c>
+      <c r="C291" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D291" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E291" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B292" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C292" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D292" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E292" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B293" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C293" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D293" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E293" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B294" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C294" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D294" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E294" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B295" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C295" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D295" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E295" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B296" t="s">
+        <v>209</v>
+      </c>
+      <c r="C296" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D296" t="s">
+        <v>210</v>
+      </c>
+      <c r="E296" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B297" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C297" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D297" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E297" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B298" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C298" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D298" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E298" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A299" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B299" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C299" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D299" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E299" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A300" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B300" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C300" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D300" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E300" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B301" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C301" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D301" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E301" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B302" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C302" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D302" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E302" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B303" t="s">
+        <v>82</v>
+      </c>
+      <c r="C303" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D303" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E303" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B304" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C304" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D304" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E304" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B305" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C305" t="s">
+        <v>209</v>
+      </c>
+      <c r="D305" t="s">
+        <v>210</v>
+      </c>
+      <c r="E305" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B306" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C306" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D306" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E306" t="s">
+        <v>10</v>
+      </c>
+      <c r="F306" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B307" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C307" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D307" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E307" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A308" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B308" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C308" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D308" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E308" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B309" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C309" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D309" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E309" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B310" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C310" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D310" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E310" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A311" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B311" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C311" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D311" t="s">
+        <v>82</v>
+      </c>
+      <c r="E311" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A312" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B312" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C312" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D312" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E312" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A348"/>
+      <c r="B348"/>
+      <c r="C348"/>
+      <c r="D348"/>
+      <c r="E348"/>
+    </row>
+    <row r="354" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A354"/>
+      <c r="B354"/>
+      <c r="C354"/>
+      <c r="D354"/>
+      <c r="E354"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E493" xr:uid="{AA7778BF-C4D9-8B46-A8CD-4B3F292AD9D0}"/>
+  <autoFilter ref="A1:E514" xr:uid="{AA7778BF-C4D9-8B46-A8CD-4B3F292AD9D0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>